--- a/templates/samples/SALES_REPORT_SAMPLE.xlsx
+++ b/templates/samples/SALES_REPORT_SAMPLE.xlsx
@@ -400,7 +400,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:O27"/>
+  <dimension ref="A1:O28"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -1671,9 +1671,56 @@
         <v/>
       </c>
     </row>
+    <row r="28">
+      <c r="A28" t="str">
+        <v>2026-07-24</v>
+      </c>
+      <c r="B28" t="str">
+        <v>AMA-SHS-1</v>
+      </c>
+      <c r="C28" t="str">
+        <v>IPH-64GB-GRA</v>
+      </c>
+      <c r="D28" t="str">
+        <v>350100000000000</v>
+      </c>
+      <c r="E28" t="str">
+        <v>NORTHSIDE STOCK</v>
+      </c>
+      <c r="F28">
+        <v>1</v>
+      </c>
+      <c r="G28">
+        <v>206.45</v>
+      </c>
+      <c r="H28">
+        <v>268.39</v>
+      </c>
+      <c r="I28">
+        <v>61.94</v>
+      </c>
+      <c r="J28" t="str">
+        <v/>
+      </c>
+      <c r="K28" t="str">
+        <v/>
+      </c>
+      <c r="L28">
+        <v>8</v>
+      </c>
+      <c r="M28" t="str">
+        <v/>
+      </c>
+      <c r="N28" t="str">
+        <v/>
+      </c>
+      <c r="O28" t="str">
+        <v/>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:O27"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:O28"/>
   </ignoredErrors>
 </worksheet>
 </file>

--- a/templates/samples/SALES_REPORT_SAMPLE.xlsx
+++ b/templates/samples/SALES_REPORT_SAMPLE.xlsx
@@ -404,7 +404,7 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
-        <v>nw</v>
+        <v>Date</v>
       </c>
       <c r="B1" t="str">
         <v>Order Number</v>

--- a/templates/samples/SALES_REPORT_SAMPLE.xlsx
+++ b/templates/samples/SALES_REPORT_SAMPLE.xlsx
@@ -1682,7 +1682,7 @@
         <v>IPH-64GB-GRA</v>
       </c>
       <c r="D28" t="str">
-        <v>350100000000000</v>
+        <v>350190000007777</v>
       </c>
       <c r="E28" t="str">
         <v>NORTHSIDE STOCK</v>

--- a/templates/samples/SALES_REPORT_SAMPLE.xlsx
+++ b/templates/samples/SALES_REPORT_SAMPLE.xlsx
@@ -7,6 +7,7 @@
     <sheet name="BM" sheetId="2" r:id="rId2"/>
     <sheet name="EBAY" sheetId="3" r:id="rId3"/>
     <sheet name="ONBUY" sheetId="4" r:id="rId4"/>
+    <sheet name="TEMU" sheetId="5" r:id="rId5"/>
   </sheets>
 </workbook>
 </file>
@@ -400,7 +401,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:O28"/>
+  <dimension ref="A1:O23"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -498,16 +499,16 @@
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>2026-07-05</v>
+        <v>2026-07-06</v>
       </c>
       <c r="B3" t="str">
-        <v>AMA-5004</v>
+        <v>AMA-5005</v>
       </c>
       <c r="C3" t="str">
-        <v>IPH-256GB-PUR</v>
+        <v>SAM-128GB-MID</v>
       </c>
       <c r="D3" t="str">
-        <v>350100000031676</v>
+        <v>350100000039595</v>
       </c>
       <c r="E3" t="str">
         <v>NORTHSIDE STOCK</v>
@@ -516,13 +517,13 @@
         <v>1</v>
       </c>
       <c r="G3">
-        <v>459.49</v>
+        <v>261.54</v>
       </c>
       <c r="H3">
-        <v>653.1</v>
+        <v>348.93</v>
       </c>
       <c r="I3">
-        <v>193.61</v>
+        <v>87.38999999999999</v>
       </c>
       <c r="J3" t="str">
         <v/>
@@ -545,16 +546,16 @@
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>2026-07-09</v>
+        <v>2026-07-11</v>
       </c>
       <c r="B4" t="str">
-        <v>AMA-5008</v>
+        <v>AMA-5010</v>
       </c>
       <c r="C4" t="str">
-        <v>IPH-64GB-PUR</v>
+        <v>IPH-128GB-GRE</v>
       </c>
       <c r="D4" t="str">
-        <v>350100000063352</v>
+        <v>350100000079190</v>
       </c>
       <c r="E4" t="str">
         <v>PHONEBOX DIRECT</v>
@@ -563,13 +564,13 @@
         <v>1</v>
       </c>
       <c r="G4">
-        <v>196.74</v>
+        <v>311.8</v>
       </c>
       <c r="H4">
-        <v>279.91</v>
+        <v>464.89</v>
       </c>
       <c r="I4">
-        <v>83.17000000000002</v>
+        <v>153.08999999999997</v>
       </c>
       <c r="J4" t="str">
         <v/>
@@ -592,31 +593,31 @@
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>2026-07-13</v>
+        <v>2026-07-16</v>
       </c>
       <c r="B5" t="str">
-        <v>AMA-5012</v>
+        <v>AMA-5015</v>
       </c>
       <c r="C5" t="str">
-        <v>SAM-128GB-BLU</v>
+        <v>GOO-128GB-BLA</v>
       </c>
       <c r="D5" t="str">
-        <v>350100000102947</v>
+        <v>350100000118785</v>
       </c>
       <c r="E5" t="str">
-        <v>MOBILE WHOLESALE LTD</v>
+        <v>PHONEBOX DIRECT</v>
       </c>
       <c r="F5">
         <v>1</v>
       </c>
       <c r="G5">
-        <v>230.57</v>
+        <v>280.37</v>
       </c>
       <c r="H5">
-        <v>342.69</v>
+        <v>392.6</v>
       </c>
       <c r="I5">
-        <v>112.12</v>
+        <v>112.23000000000002</v>
       </c>
       <c r="J5" t="str">
         <v/>
@@ -625,7 +626,7 @@
         <v/>
       </c>
       <c r="L5">
-        <v>6.3</v>
+        <v>8</v>
       </c>
       <c r="M5" t="str">
         <v/>
@@ -639,31 +640,31 @@
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>2026-07-17</v>
+        <v>2026-07-21</v>
       </c>
       <c r="B6" t="str">
-        <v>AMA-5016</v>
+        <v>AMA-5020</v>
       </c>
       <c r="C6" t="str">
-        <v>IPH-64GB-MID</v>
+        <v>IPH-256GB-GRE</v>
       </c>
       <c r="D6" t="str">
-        <v>350100000126704</v>
+        <v>350100000158380</v>
       </c>
       <c r="E6" t="str">
-        <v>MOBILE WHOLESALE LTD</v>
+        <v>CELLHUB TRADING</v>
       </c>
       <c r="F6">
         <v>1</v>
       </c>
       <c r="G6">
-        <v>212.15</v>
+        <v>469.17</v>
       </c>
       <c r="H6">
-        <v>297.07</v>
+        <v>662.93</v>
       </c>
       <c r="I6">
-        <v>84.91999999999999</v>
+        <v>193.75999999999993</v>
       </c>
       <c r="J6" t="str">
         <v/>
@@ -672,7 +673,7 @@
         <v/>
       </c>
       <c r="L6">
-        <v>8</v>
+        <v>6.3</v>
       </c>
       <c r="M6" t="str">
         <v/>
@@ -686,31 +687,31 @@
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>2026-07-21</v>
+        <v>2026-07-02</v>
       </c>
       <c r="B7" t="str">
-        <v>AMA-5020</v>
+        <v>AMA-5025</v>
       </c>
       <c r="C7" t="str">
-        <v>IPH-256GB-GRE</v>
+        <v>IPH-128GB-STA</v>
       </c>
       <c r="D7" t="str">
-        <v>350100000158380</v>
+        <v>350100000197975</v>
       </c>
       <c r="E7" t="str">
-        <v>CELLHUB TRADING</v>
+        <v>PHONEBOX DIRECT</v>
       </c>
       <c r="F7">
         <v>1</v>
       </c>
       <c r="G7">
-        <v>469.17</v>
+        <v>233.36</v>
       </c>
       <c r="H7">
-        <v>656.42</v>
+        <v>318.95</v>
       </c>
       <c r="I7">
-        <v>187.24999999999994</v>
+        <v>85.58999999999997</v>
       </c>
       <c r="J7" t="str">
         <v/>
@@ -719,7 +720,7 @@
         <v/>
       </c>
       <c r="L7">
-        <v>8</v>
+        <v>6.3</v>
       </c>
       <c r="M7" t="str">
         <v/>
@@ -733,31 +734,31 @@
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>2026-07-01</v>
+        <v>2026-07-07</v>
       </c>
       <c r="B8" t="str">
-        <v>AMA-5024</v>
+        <v>AMA-5030</v>
       </c>
       <c r="C8" t="str">
-        <v>IPH-128GB-STA</v>
+        <v>SAM-256GB-GRA</v>
       </c>
       <c r="D8" t="str">
-        <v>350100000197975</v>
+        <v>350100000237570</v>
       </c>
       <c r="E8" t="str">
-        <v>PHONEBOX DIRECT</v>
+        <v>MOBILE WHOLESALE LTD</v>
       </c>
       <c r="F8">
         <v>1</v>
       </c>
       <c r="G8">
-        <v>233.36</v>
+        <v>418.34</v>
       </c>
       <c r="H8">
-        <v>325.62</v>
+        <v>600.73</v>
       </c>
       <c r="I8">
-        <v>92.25999999999999</v>
+        <v>182.39000000000004</v>
       </c>
       <c r="J8" t="str">
         <v/>
@@ -780,31 +781,31 @@
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>2026-07-05</v>
+        <v>2026-07-12</v>
       </c>
       <c r="B9" t="str">
-        <v>AMA-5028</v>
+        <v>AMA-5035</v>
       </c>
       <c r="C9" t="str">
-        <v>IPH-256GB-GRA</v>
+        <v>IPH-256GB-GRE</v>
       </c>
       <c r="D9" t="str">
-        <v>350100000221732</v>
+        <v>350100000277165</v>
       </c>
       <c r="E9" t="str">
-        <v>PHONEBOX DIRECT</v>
+        <v>CELLHUB TRADING</v>
       </c>
       <c r="F9">
         <v>1</v>
       </c>
       <c r="G9">
-        <v>499.6</v>
+        <v>495.98</v>
       </c>
       <c r="H9">
-        <v>721.92</v>
+        <v>737.52</v>
       </c>
       <c r="I9">
-        <v>222.31999999999994</v>
+        <v>241.53999999999996</v>
       </c>
       <c r="J9" t="str">
         <v/>
@@ -813,7 +814,7 @@
         <v/>
       </c>
       <c r="L9">
-        <v>2</v>
+        <v>6.3</v>
       </c>
       <c r="M9" t="str">
         <v/>
@@ -827,31 +828,31 @@
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>2026-07-09</v>
+        <v>2026-07-17</v>
       </c>
       <c r="B10" t="str">
-        <v>AMA-5032</v>
+        <v>AMA-5040</v>
       </c>
       <c r="C10" t="str">
-        <v>IPH-64GB-GRE</v>
+        <v>IPH-64GB-WHI</v>
       </c>
       <c r="D10" t="str">
-        <v>350100000253408</v>
+        <v>350100000316760</v>
       </c>
       <c r="E10" t="str">
-        <v>PHONEBOX DIRECT</v>
+        <v>MOBILE WHOLESALE LTD</v>
       </c>
       <c r="F10">
         <v>1</v>
       </c>
       <c r="G10">
-        <v>196.32</v>
+        <v>192.93</v>
       </c>
       <c r="H10">
-        <v>281.91</v>
+        <v>288.15</v>
       </c>
       <c r="I10">
-        <v>85.59000000000003</v>
+        <v>95.21999999999997</v>
       </c>
       <c r="J10" t="str">
         <v/>
@@ -874,31 +875,31 @@
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>2026-07-13</v>
+        <v>2026-07-22</v>
       </c>
       <c r="B11" t="str">
-        <v>AMA-5036</v>
+        <v>AMA-5045</v>
       </c>
       <c r="C11" t="str">
-        <v>SAM-128GB-GRE</v>
+        <v>SAM-128GB-MID</v>
       </c>
       <c r="D11" t="str">
-        <v>350100000293003</v>
+        <v>350100000356355</v>
       </c>
       <c r="E11" t="str">
-        <v>MOBILE WHOLESALE LTD</v>
+        <v>CELLHUB TRADING</v>
       </c>
       <c r="F11">
         <v>1</v>
       </c>
       <c r="G11">
-        <v>262.94</v>
+        <v>237.5</v>
       </c>
       <c r="H11">
-        <v>336.47</v>
+        <v>333.23</v>
       </c>
       <c r="I11">
-        <v>73.53000000000003</v>
+        <v>95.73000000000002</v>
       </c>
       <c r="J11" t="str">
         <v/>
@@ -921,31 +922,31 @@
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>2026-07-17</v>
+        <v>2026-07-03</v>
       </c>
       <c r="B12" t="str">
-        <v>AMA-5040</v>
+        <v>AMA-5050</v>
       </c>
       <c r="C12" t="str">
-        <v>IPH-64GB-WHI</v>
+        <v>IPH-128GB-BLU</v>
       </c>
       <c r="D12" t="str">
-        <v>350100000316760</v>
+        <v>350100000395950</v>
       </c>
       <c r="E12" t="str">
-        <v>MOBILE WHOLESALE LTD</v>
+        <v>PHONEBOX DIRECT</v>
       </c>
       <c r="F12">
         <v>1</v>
       </c>
       <c r="G12">
-        <v>192.93</v>
+        <v>316.67</v>
       </c>
       <c r="H12">
-        <v>286.77</v>
+        <v>443.11</v>
       </c>
       <c r="I12">
-        <v>93.83999999999997</v>
+        <v>126.44</v>
       </c>
       <c r="J12" t="str">
         <v/>
@@ -954,7 +955,7 @@
         <v/>
       </c>
       <c r="L12">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="M12" t="str">
         <v/>
@@ -968,16 +969,16 @@
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>2026-07-21</v>
+        <v>2026-07-08</v>
       </c>
       <c r="B13" t="str">
-        <v>AMA-5044</v>
+        <v>AMA-5055</v>
       </c>
       <c r="C13" t="str">
-        <v>IPH-256GB-MID</v>
+        <v>GOO-128GB-MID</v>
       </c>
       <c r="D13" t="str">
-        <v>350100000348436</v>
+        <v>350100000435545</v>
       </c>
       <c r="E13" t="str">
         <v>MOBILE WHOLESALE LTD</v>
@@ -986,13 +987,13 @@
         <v>1</v>
       </c>
       <c r="G13">
-        <v>484.06</v>
+        <v>267</v>
       </c>
       <c r="H13">
-        <v>718.37</v>
+        <v>377.39</v>
       </c>
       <c r="I13">
-        <v>234.31</v>
+        <v>110.38999999999999</v>
       </c>
       <c r="J13" t="str">
         <v/>
@@ -1015,31 +1016,31 @@
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>2026-07-01</v>
+        <v>2026-07-13</v>
       </c>
       <c r="B14" t="str">
-        <v>AMA-5048</v>
+        <v>AMA-5060</v>
       </c>
       <c r="C14" t="str">
-        <v>IPH-128GB-BLA</v>
+        <v>SAM-128GB-WHI</v>
       </c>
       <c r="D14" t="str">
-        <v>350100000388031</v>
+        <v>350100000483059</v>
       </c>
       <c r="E14" t="str">
-        <v>NORTHSIDE STOCK</v>
+        <v>MOBILE WHOLESALE LTD</v>
       </c>
       <c r="F14">
         <v>1</v>
       </c>
       <c r="G14">
-        <v>232.81</v>
+        <v>250.16</v>
       </c>
       <c r="H14">
-        <v>326.65</v>
+        <v>335.89</v>
       </c>
       <c r="I14">
-        <v>93.83999999999997</v>
+        <v>85.72999999999999</v>
       </c>
       <c r="J14" t="str">
         <v/>
@@ -1062,31 +1063,31 @@
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>2026-07-05</v>
+        <v>2026-07-18</v>
       </c>
       <c r="B15" t="str">
-        <v>AMA-5052</v>
+        <v>AMA-5065</v>
       </c>
       <c r="C15" t="str">
-        <v>IPH-256GB-PUR</v>
+        <v>IPH-128GB-WHI</v>
       </c>
       <c r="D15" t="str">
-        <v>350100000411788</v>
+        <v>350100000514735</v>
       </c>
       <c r="E15" t="str">
-        <v>MOBILE WHOLESALE LTD</v>
+        <v>PHONEBOX DIRECT</v>
       </c>
       <c r="F15">
         <v>1</v>
       </c>
       <c r="G15">
-        <v>497.17</v>
+        <v>222.24</v>
       </c>
       <c r="H15">
-        <v>681.49</v>
+        <v>294.66</v>
       </c>
       <c r="I15">
-        <v>184.32</v>
+        <v>72.42000000000002</v>
       </c>
       <c r="J15" t="str">
         <v/>
@@ -1095,7 +1096,7 @@
         <v/>
       </c>
       <c r="L15">
-        <v>8</v>
+        <v>6.3</v>
       </c>
       <c r="M15" t="str">
         <v/>
@@ -1109,31 +1110,31 @@
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>2026-07-09</v>
+        <v>2026-07-23</v>
       </c>
       <c r="B16" t="str">
-        <v>AMA-5056</v>
+        <v>AMA-5070</v>
       </c>
       <c r="C16" t="str">
-        <v>IPH-64GB-MID</v>
+        <v>SAM-256GB-GRA</v>
       </c>
       <c r="D16" t="str">
-        <v>350100000443464</v>
+        <v>350100000554330</v>
       </c>
       <c r="E16" t="str">
-        <v>MOBILE WHOLESALE LTD</v>
+        <v>CELLHUB TRADING</v>
       </c>
       <c r="F16">
         <v>1</v>
       </c>
       <c r="G16">
-        <v>194.75</v>
+        <v>451.39</v>
       </c>
       <c r="H16">
-        <v>269.01</v>
+        <v>574.19</v>
       </c>
       <c r="I16">
-        <v>74.25999999999999</v>
+        <v>122.80000000000007</v>
       </c>
       <c r="J16" t="str">
         <v/>
@@ -1142,7 +1143,7 @@
         <v/>
       </c>
       <c r="L16">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="M16" t="str">
         <v/>
@@ -1156,31 +1157,31 @@
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v>2026-07-13</v>
+        <v>2026-07-04</v>
       </c>
       <c r="B17" t="str">
-        <v>AMA-5060</v>
+        <v>AMA-5075</v>
       </c>
       <c r="C17" t="str">
-        <v>SAM-128GB-WHI</v>
+        <v>IPH-256GB-BLA</v>
       </c>
       <c r="D17" t="str">
-        <v>350100000483059</v>
+        <v>350100000593925</v>
       </c>
       <c r="E17" t="str">
-        <v>MOBILE WHOLESALE LTD</v>
+        <v>NORTHSIDE STOCK</v>
       </c>
       <c r="F17">
         <v>1</v>
       </c>
       <c r="G17">
-        <v>250.16</v>
+        <v>501.14</v>
       </c>
       <c r="H17">
-        <v>325.93</v>
+        <v>631.55</v>
       </c>
       <c r="I17">
-        <v>75.77000000000001</v>
+        <v>130.40999999999997</v>
       </c>
       <c r="J17" t="str">
         <v/>
@@ -1203,16 +1204,16 @@
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v>2026-07-17</v>
+        <v>2026-07-09</v>
       </c>
       <c r="B18" t="str">
-        <v>AMA-5064</v>
+        <v>AMA-5080</v>
       </c>
       <c r="C18" t="str">
-        <v>IPH-64GB-GRE</v>
+        <v>IPH-64GB-WHI</v>
       </c>
       <c r="D18" t="str">
-        <v>350100000506816</v>
+        <v>350100000633520</v>
       </c>
       <c r="E18" t="str">
         <v>MOBILE WHOLESALE LTD</v>
@@ -1221,13 +1222,13 @@
         <v>1</v>
       </c>
       <c r="G18">
-        <v>197.28</v>
+        <v>190.34</v>
       </c>
       <c r="H18">
-        <v>264.89</v>
+        <v>275.79</v>
       </c>
       <c r="I18">
-        <v>67.60999999999999</v>
+        <v>85.45000000000002</v>
       </c>
       <c r="J18" t="str">
         <v/>
@@ -1236,7 +1237,7 @@
         <v/>
       </c>
       <c r="L18">
-        <v>8</v>
+        <v>6.3</v>
       </c>
       <c r="M18" t="str">
         <v/>
@@ -1250,31 +1251,31 @@
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v>2026-07-21</v>
+        <v>2026-07-14</v>
       </c>
       <c r="B19" t="str">
-        <v>AMA-5068</v>
+        <v>AMA-5085</v>
       </c>
       <c r="C19" t="str">
-        <v>IPH-256GB-MID</v>
+        <v>SAM-128GB-GRA</v>
       </c>
       <c r="D19" t="str">
-        <v>350100000538492</v>
+        <v>350100000673115</v>
       </c>
       <c r="E19" t="str">
-        <v>MOBILE WHOLESALE LTD</v>
+        <v>NORTHSIDE STOCK</v>
       </c>
       <c r="F19">
         <v>1</v>
       </c>
       <c r="G19">
-        <v>482.51</v>
+        <v>246.21</v>
       </c>
       <c r="H19">
-        <v>620.19</v>
+        <v>319.55</v>
       </c>
       <c r="I19">
-        <v>137.68000000000006</v>
+        <v>73.34</v>
       </c>
       <c r="J19" t="str">
         <v/>
@@ -1297,31 +1298,31 @@
     </row>
     <row r="20">
       <c r="A20" t="str">
-        <v>2026-07-01</v>
+        <v>2026-07-19</v>
       </c>
       <c r="B20" t="str">
-        <v>AMA-5072</v>
+        <v>AMA-5090</v>
       </c>
       <c r="C20" t="str">
-        <v>IPH-128GB-MID</v>
+        <v>IPH-128GB-GRA</v>
       </c>
       <c r="D20" t="str">
-        <v>350100000578087</v>
+        <v>350100007839810</v>
       </c>
       <c r="E20" t="str">
-        <v>NORTHSIDE STOCK</v>
+        <v>PHONEBOX DIRECT</v>
       </c>
       <c r="F20">
         <v>1</v>
       </c>
       <c r="G20">
-        <v>222.91</v>
+        <v>335.04</v>
       </c>
       <c r="H20">
-        <v>285.35</v>
+        <v>494.65</v>
       </c>
       <c r="I20">
-        <v>62.440000000000026</v>
+        <v>159.60999999999996</v>
       </c>
       <c r="J20" t="str">
         <v/>
@@ -1330,7 +1331,7 @@
         <v/>
       </c>
       <c r="L20">
-        <v>8</v>
+        <v>6.3</v>
       </c>
       <c r="M20" t="str">
         <v/>
@@ -1344,16 +1345,16 @@
     </row>
     <row r="21">
       <c r="A21" t="str">
-        <v>2026-07-05</v>
+        <v>2026-07-24</v>
       </c>
       <c r="B21" t="str">
-        <v>AMA-5076</v>
+        <v>AMA-5095</v>
       </c>
       <c r="C21" t="str">
-        <v>IPH-256GB-STA</v>
+        <v>GOO-128GB-BLU</v>
       </c>
       <c r="D21" t="str">
-        <v>350100000601844</v>
+        <v>350100007879405</v>
       </c>
       <c r="E21" t="str">
         <v>MOBILE WHOLESALE LTD</v>
@@ -1362,13 +1363,13 @@
         <v>1</v>
       </c>
       <c r="G21">
-        <v>476.5</v>
+        <v>293.74</v>
       </c>
       <c r="H21">
-        <v>688.88</v>
+        <v>406.06</v>
       </c>
       <c r="I21">
-        <v>212.38</v>
+        <v>112.32</v>
       </c>
       <c r="J21" t="str">
         <v/>
@@ -1391,31 +1392,31 @@
     </row>
     <row r="22">
       <c r="A22" t="str">
-        <v>2026-07-09</v>
+        <v>2026-07-01</v>
       </c>
       <c r="B22" t="str">
-        <v>AMA-5080</v>
+        <v>AMA-5000</v>
       </c>
       <c r="C22" t="str">
-        <v>IPH-64GB-WHI</v>
+        <v>IPH-128GB-GRA</v>
       </c>
       <c r="D22" t="str">
-        <v>350100000633520</v>
+        <v>350100000007919</v>
       </c>
       <c r="E22" t="str">
-        <v>MOBILE WHOLESALE LTD</v>
+        <v>PHONEBOX DIRECT</v>
       </c>
       <c r="F22">
         <v>1</v>
       </c>
       <c r="G22">
-        <v>190.34</v>
+        <v>234.13</v>
       </c>
       <c r="H22">
-        <v>239.87</v>
+        <v>319.21</v>
       </c>
       <c r="I22">
-        <v>49.53</v>
+        <v>85.07999999999998</v>
       </c>
       <c r="J22" t="str">
         <v/>
@@ -1424,7 +1425,7 @@
         <v/>
       </c>
       <c r="L22">
-        <v>6.3</v>
+        <v>8</v>
       </c>
       <c r="M22" t="str">
         <v/>
@@ -1438,16 +1439,16 @@
     </row>
     <row r="23">
       <c r="A23" t="str">
-        <v>2026-07-13</v>
+        <v>2026-07-24</v>
       </c>
       <c r="B23" t="str">
-        <v>AMA-5084</v>
+        <v>AMA-SHS-1</v>
       </c>
       <c r="C23" t="str">
-        <v>SAM-128GB-GRA</v>
+        <v>IPH-64GB-GRA</v>
       </c>
       <c r="D23" t="str">
-        <v>350100000673115</v>
+        <v>350190000007777</v>
       </c>
       <c r="E23" t="str">
         <v>NORTHSIDE STOCK</v>
@@ -1456,13 +1457,13 @@
         <v>1</v>
       </c>
       <c r="G23">
-        <v>246.21</v>
+        <v>206.45</v>
       </c>
       <c r="H23">
-        <v>318</v>
+        <v>268.39</v>
       </c>
       <c r="I23">
-        <v>71.78999999999999</v>
+        <v>61.94</v>
       </c>
       <c r="J23" t="str">
         <v/>
@@ -1471,7 +1472,7 @@
         <v/>
       </c>
       <c r="L23">
-        <v>6.3</v>
+        <v>8</v>
       </c>
       <c r="M23" t="str">
         <v/>
@@ -1480,254 +1481,19 @@
         <v/>
       </c>
       <c r="O23" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="str">
-        <v>2026-07-17</v>
-      </c>
-      <c r="B24" t="str">
-        <v>AMA-5088</v>
-      </c>
-      <c r="C24" t="str">
-        <v>IPH-64GB-STA</v>
-      </c>
-      <c r="D24" t="str">
-        <v>350100000696872</v>
-      </c>
-      <c r="E24" t="str">
-        <v>NORTHSIDE STOCK</v>
-      </c>
-      <c r="F24">
-        <v>1</v>
-      </c>
-      <c r="G24">
-        <v>186.57</v>
-      </c>
-      <c r="H24">
-        <v>239.7</v>
-      </c>
-      <c r="I24">
-        <v>53.129999999999995</v>
-      </c>
-      <c r="J24" t="str">
-        <v/>
-      </c>
-      <c r="K24" t="str">
-        <v/>
-      </c>
-      <c r="L24">
-        <v>8</v>
-      </c>
-      <c r="M24" t="str">
-        <v/>
-      </c>
-      <c r="N24" t="str">
-        <v/>
-      </c>
-      <c r="O24" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="str">
-        <v>2026-07-21</v>
-      </c>
-      <c r="B25" t="str">
-        <v>AMA-5092</v>
-      </c>
-      <c r="C25" t="str">
-        <v>IPH-256GB-GRA</v>
-      </c>
-      <c r="D25" t="str">
-        <v>350100007855648</v>
-      </c>
-      <c r="E25" t="str">
-        <v>PHONEBOX DIRECT</v>
-      </c>
-      <c r="F25">
-        <v>1</v>
-      </c>
-      <c r="G25">
-        <v>462.92</v>
-      </c>
-      <c r="H25">
-        <v>615.58</v>
-      </c>
-      <c r="I25">
-        <v>152.66000000000003</v>
-      </c>
-      <c r="J25" t="str">
-        <v/>
-      </c>
-      <c r="K25" t="str">
-        <v/>
-      </c>
-      <c r="L25">
-        <v>2</v>
-      </c>
-      <c r="M25" t="str">
-        <v/>
-      </c>
-      <c r="N25" t="str">
-        <v/>
-      </c>
-      <c r="O25" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="str">
-        <v>2026-07-01</v>
-      </c>
-      <c r="B26" t="str">
-        <v>AMA-5096</v>
-      </c>
-      <c r="C26" t="str">
-        <v>IPH-128GB-GRA</v>
-      </c>
-      <c r="D26" t="str">
-        <v>350100007887324</v>
-      </c>
-      <c r="E26" t="str">
-        <v>PHONEBOX DIRECT</v>
-      </c>
-      <c r="F26">
-        <v>1</v>
-      </c>
-      <c r="G26">
-        <v>223.04</v>
-      </c>
-      <c r="H26">
-        <v>329.29</v>
-      </c>
-      <c r="I26">
-        <v>106.25000000000003</v>
-      </c>
-      <c r="J26" t="str">
-        <v/>
-      </c>
-      <c r="K26" t="str">
-        <v/>
-      </c>
-      <c r="L26">
-        <v>6.3</v>
-      </c>
-      <c r="M26" t="str">
-        <v/>
-      </c>
-      <c r="N26" t="str">
-        <v/>
-      </c>
-      <c r="O26" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="str">
-        <v>2026-07-01</v>
-      </c>
-      <c r="B27" t="str">
-        <v>AMA-5000</v>
-      </c>
-      <c r="C27" t="str">
-        <v>IPH-128GB-GRA</v>
-      </c>
-      <c r="D27" t="str">
-        <v>350100000007919</v>
-      </c>
-      <c r="E27" t="str">
-        <v>PHONEBOX DIRECT</v>
-      </c>
-      <c r="F27">
-        <v>1</v>
-      </c>
-      <c r="G27">
-        <v>234.13</v>
-      </c>
-      <c r="H27">
-        <v>319.21</v>
-      </c>
-      <c r="I27">
-        <v>85.07999999999998</v>
-      </c>
-      <c r="J27" t="str">
-        <v/>
-      </c>
-      <c r="K27" t="str">
-        <v/>
-      </c>
-      <c r="L27">
-        <v>8</v>
-      </c>
-      <c r="M27" t="str">
-        <v/>
-      </c>
-      <c r="N27" t="str">
-        <v/>
-      </c>
-      <c r="O27" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="str">
-        <v>2026-07-24</v>
-      </c>
-      <c r="B28" t="str">
-        <v>AMA-SHS-1</v>
-      </c>
-      <c r="C28" t="str">
-        <v>IPH-64GB-GRA</v>
-      </c>
-      <c r="D28" t="str">
-        <v>350190000007777</v>
-      </c>
-      <c r="E28" t="str">
-        <v>NORTHSIDE STOCK</v>
-      </c>
-      <c r="F28">
-        <v>1</v>
-      </c>
-      <c r="G28">
-        <v>206.45</v>
-      </c>
-      <c r="H28">
-        <v>268.39</v>
-      </c>
-      <c r="I28">
-        <v>61.94</v>
-      </c>
-      <c r="J28" t="str">
-        <v/>
-      </c>
-      <c r="K28" t="str">
-        <v/>
-      </c>
-      <c r="L28">
-        <v>8</v>
-      </c>
-      <c r="M28" t="str">
-        <v/>
-      </c>
-      <c r="N28" t="str">
-        <v/>
-      </c>
-      <c r="O28" t="str">
         <v/>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:O28"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:O23"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Q26"/>
+  <dimension ref="A1:Q21"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -1837,34 +1603,34 @@
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>2026-07-06</v>
+        <v>2026-07-07</v>
       </c>
       <c r="B3" t="str">
-        <v>BM-5005</v>
+        <v>BM-5006</v>
       </c>
       <c r="C3" t="str">
-        <v>SAM-128GB-MID</v>
+        <v>SAM-256GB-WHI</v>
       </c>
       <c r="D3" t="str">
-        <v>350100000039595</v>
+        <v>350100000047514</v>
       </c>
       <c r="E3" t="str">
-        <v>NORTHSIDE STOCK</v>
+        <v>PHONEBOX DIRECT</v>
       </c>
       <c r="F3">
         <v>1</v>
       </c>
       <c r="G3">
-        <v>261.54</v>
+        <v>446.53</v>
       </c>
       <c r="H3">
-        <v>391.67</v>
+        <v>643.55</v>
       </c>
       <c r="I3" t="str">
-        <v>Card</v>
+        <v>Paypal</v>
       </c>
       <c r="J3">
-        <v>130.13</v>
+        <v>197.01999999999998</v>
       </c>
       <c r="K3" t="str">
         <v/>
@@ -1876,7 +1642,7 @@
         <v/>
       </c>
       <c r="N3">
-        <v>8</v>
+        <v>6.3</v>
       </c>
       <c r="O3" t="str">
         <v/>
@@ -1890,34 +1656,34 @@
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>2026-07-10</v>
+        <v>2026-07-12</v>
       </c>
       <c r="B4" t="str">
-        <v>BM-5009</v>
+        <v>BM-5011</v>
       </c>
       <c r="C4" t="str">
-        <v>IPH-128GB-WHI</v>
+        <v>IPH-256GB-BLA</v>
       </c>
       <c r="D4" t="str">
-        <v>350100000071271</v>
+        <v>350100000087109</v>
       </c>
       <c r="E4" t="str">
-        <v>CELLHUB TRADING</v>
+        <v>MOBILE WHOLESALE LTD</v>
       </c>
       <c r="F4">
         <v>1</v>
       </c>
       <c r="G4">
-        <v>229.85</v>
+        <v>514.23</v>
       </c>
       <c r="H4">
-        <v>339.76</v>
+        <v>704.32</v>
       </c>
       <c r="I4" t="str">
-        <v>Paypal</v>
+        <v>Card</v>
       </c>
       <c r="J4">
-        <v>109.91</v>
+        <v>190.09000000000003</v>
       </c>
       <c r="K4" t="str">
         <v/>
@@ -1929,7 +1695,7 @@
         <v/>
       </c>
       <c r="N4">
-        <v>6.3</v>
+        <v>2</v>
       </c>
       <c r="O4" t="str">
         <v/>
@@ -1943,16 +1709,16 @@
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>2026-07-14</v>
+        <v>2026-07-17</v>
       </c>
       <c r="B5" t="str">
-        <v>BM-5013</v>
+        <v>BM-5016</v>
       </c>
       <c r="C5" t="str">
-        <v>SAM-128GB-BLU</v>
+        <v>IPH-64GB-MID</v>
       </c>
       <c r="D5" t="str">
-        <v>350100000102947</v>
+        <v>350100000126704</v>
       </c>
       <c r="E5" t="str">
         <v>MOBILE WHOLESALE LTD</v>
@@ -1961,16 +1727,16 @@
         <v>1</v>
       </c>
       <c r="G5">
-        <v>230.57</v>
+        <v>212.15</v>
       </c>
       <c r="H5">
-        <v>319.34</v>
+        <v>302.32</v>
       </c>
       <c r="I5" t="str">
-        <v>Klarna</v>
+        <v>Card</v>
       </c>
       <c r="J5">
-        <v>88.76999999999998</v>
+        <v>90.16999999999999</v>
       </c>
       <c r="K5" t="str">
         <v/>
@@ -1996,34 +1762,34 @@
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>2026-07-18</v>
+        <v>2026-07-22</v>
       </c>
       <c r="B6" t="str">
-        <v>BM-5017</v>
+        <v>BM-5021</v>
       </c>
       <c r="C6" t="str">
-        <v>IPH-128GB-GRA</v>
+        <v>SAM-128GB-BLU</v>
       </c>
       <c r="D6" t="str">
-        <v>350100000134623</v>
+        <v>350100000166299</v>
       </c>
       <c r="E6" t="str">
-        <v>CELLHUB TRADING</v>
+        <v>NORTHSIDE STOCK</v>
       </c>
       <c r="F6">
         <v>1</v>
       </c>
       <c r="G6">
-        <v>219.35</v>
+        <v>246.31</v>
       </c>
       <c r="H6">
-        <v>312.58</v>
+        <v>323.35</v>
       </c>
       <c r="I6" t="str">
-        <v>Card</v>
+        <v>Klarna</v>
       </c>
       <c r="J6">
-        <v>93.22999999999999</v>
+        <v>77.04000000000002</v>
       </c>
       <c r="K6" t="str">
         <v/>
@@ -2049,34 +1815,34 @@
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>2026-07-22</v>
+        <v>2026-07-03</v>
       </c>
       <c r="B7" t="str">
-        <v>BM-5021</v>
+        <v>BM-5026</v>
       </c>
       <c r="C7" t="str">
-        <v>SAM-128GB-BLU</v>
+        <v>IPH-128GB-PUR</v>
       </c>
       <c r="D7" t="str">
-        <v>350100000166299</v>
+        <v>350100000205894</v>
       </c>
       <c r="E7" t="str">
-        <v>NORTHSIDE STOCK</v>
+        <v>PHONEBOX DIRECT</v>
       </c>
       <c r="F7">
         <v>1</v>
       </c>
       <c r="G7">
-        <v>246.31</v>
+        <v>325.88</v>
       </c>
       <c r="H7">
-        <v>322.89</v>
+        <v>448.08</v>
       </c>
       <c r="I7" t="str">
-        <v>Klarna</v>
+        <v>Card</v>
       </c>
       <c r="J7">
-        <v>76.57999999999998</v>
+        <v>122.19999999999999</v>
       </c>
       <c r="K7" t="str">
         <v/>
@@ -2102,34 +1868,34 @@
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>2026-07-02</v>
+        <v>2026-07-08</v>
       </c>
       <c r="B8" t="str">
-        <v>BM-5025</v>
+        <v>BM-5031</v>
       </c>
       <c r="C8" t="str">
-        <v>IPH-128GB-STA</v>
+        <v>GOO-128GB-GRE</v>
       </c>
       <c r="D8" t="str">
-        <v>350100000197975</v>
+        <v>350100000245489</v>
       </c>
       <c r="E8" t="str">
-        <v>PHONEBOX DIRECT</v>
+        <v>MOBILE WHOLESALE LTD</v>
       </c>
       <c r="F8">
         <v>1</v>
       </c>
       <c r="G8">
-        <v>233.36</v>
+        <v>290.37</v>
       </c>
       <c r="H8">
-        <v>340.98</v>
+        <v>415.64</v>
       </c>
       <c r="I8" t="str">
-        <v>Paypal</v>
+        <v>Klarna</v>
       </c>
       <c r="J8">
-        <v>107.62</v>
+        <v>125.26999999999998</v>
       </c>
       <c r="K8" t="str">
         <v/>
@@ -2155,34 +1921,34 @@
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>2026-07-06</v>
+        <v>2026-07-13</v>
       </c>
       <c r="B9" t="str">
-        <v>BM-5029</v>
+        <v>BM-5036</v>
       </c>
       <c r="C9" t="str">
-        <v>SAM-128GB-WHI</v>
+        <v>SAM-128GB-GRE</v>
       </c>
       <c r="D9" t="str">
-        <v>350100000229651</v>
+        <v>350100000293003</v>
       </c>
       <c r="E9" t="str">
-        <v>NORTHSIDE STOCK</v>
+        <v>MOBILE WHOLESALE LTD</v>
       </c>
       <c r="F9">
         <v>1</v>
       </c>
       <c r="G9">
-        <v>253.86</v>
+        <v>262.94</v>
       </c>
       <c r="H9">
-        <v>368.99</v>
+        <v>388.08</v>
       </c>
       <c r="I9" t="str">
-        <v>Paypal</v>
+        <v>Klarna</v>
       </c>
       <c r="J9">
-        <v>115.13</v>
+        <v>125.13999999999999</v>
       </c>
       <c r="K9" t="str">
         <v/>
@@ -2208,34 +1974,34 @@
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>2026-07-10</v>
+        <v>2026-07-18</v>
       </c>
       <c r="B10" t="str">
-        <v>BM-5033</v>
+        <v>BM-5041</v>
       </c>
       <c r="C10" t="str">
-        <v>IPH-128GB-GRE</v>
+        <v>IPH-128GB-MID</v>
       </c>
       <c r="D10" t="str">
-        <v>350100000261327</v>
+        <v>350100000324679</v>
       </c>
       <c r="E10" t="str">
-        <v>CELLHUB TRADING</v>
+        <v>PHONEBOX DIRECT</v>
       </c>
       <c r="F10">
         <v>1</v>
       </c>
       <c r="G10">
-        <v>209.59</v>
+        <v>232.24</v>
       </c>
       <c r="H10">
-        <v>300.01</v>
+        <v>310.64</v>
       </c>
       <c r="I10" t="str">
-        <v>Klarna</v>
+        <v>Paypal</v>
       </c>
       <c r="J10">
-        <v>90.41999999999999</v>
+        <v>78.39999999999998</v>
       </c>
       <c r="K10" t="str">
         <v/>
@@ -2247,7 +2013,7 @@
         <v/>
       </c>
       <c r="N10">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="O10" t="str">
         <v/>
@@ -2261,16 +2027,16 @@
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>2026-07-14</v>
+        <v>2026-07-23</v>
       </c>
       <c r="B11" t="str">
-        <v>BM-5037</v>
+        <v>BM-5046</v>
       </c>
       <c r="C11" t="str">
-        <v>SAM-128GB-GRE</v>
+        <v>SAM-256GB-PUR</v>
       </c>
       <c r="D11" t="str">
-        <v>350100000293003</v>
+        <v>350100000364274</v>
       </c>
       <c r="E11" t="str">
         <v>MOBILE WHOLESALE LTD</v>
@@ -2279,16 +2045,16 @@
         <v>1</v>
       </c>
       <c r="G11">
-        <v>262.94</v>
+        <v>453.75</v>
       </c>
       <c r="H11">
-        <v>359.97</v>
+        <v>609.97</v>
       </c>
       <c r="I11" t="str">
-        <v>Card</v>
+        <v>Klarna</v>
       </c>
       <c r="J11">
-        <v>97.03000000000003</v>
+        <v>156.22000000000003</v>
       </c>
       <c r="K11" t="str">
         <v/>
@@ -2314,16 +2080,16 @@
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>2026-07-18</v>
+        <v>2026-07-04</v>
       </c>
       <c r="B12" t="str">
-        <v>BM-5041</v>
+        <v>BM-5051</v>
       </c>
       <c r="C12" t="str">
-        <v>IPH-128GB-MID</v>
+        <v>IPH-256GB-GRE</v>
       </c>
       <c r="D12" t="str">
-        <v>350100000324679</v>
+        <v>350100000403869</v>
       </c>
       <c r="E12" t="str">
         <v>PHONEBOX DIRECT</v>
@@ -2332,16 +2098,16 @@
         <v>1</v>
       </c>
       <c r="G12">
-        <v>232.24</v>
+        <v>533.2</v>
       </c>
       <c r="H12">
-        <v>312.85</v>
+        <v>791.22</v>
       </c>
       <c r="I12" t="str">
-        <v>Paypal</v>
+        <v>Klarna</v>
       </c>
       <c r="J12">
-        <v>80.61000000000001</v>
+        <v>258.02</v>
       </c>
       <c r="K12" t="str">
         <v/>
@@ -2367,34 +2133,34 @@
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>2026-07-22</v>
+        <v>2026-07-09</v>
       </c>
       <c r="B13" t="str">
-        <v>BM-5045</v>
+        <v>BM-5056</v>
       </c>
       <c r="C13" t="str">
-        <v>SAM-128GB-MID</v>
+        <v>IPH-64GB-MID</v>
       </c>
       <c r="D13" t="str">
-        <v>350100000356355</v>
+        <v>350100000443464</v>
       </c>
       <c r="E13" t="str">
-        <v>CELLHUB TRADING</v>
+        <v>MOBILE WHOLESALE LTD</v>
       </c>
       <c r="F13">
         <v>1</v>
       </c>
       <c r="G13">
-        <v>237.5</v>
+        <v>194.75</v>
       </c>
       <c r="H13">
-        <v>306.63</v>
+        <v>250.75</v>
       </c>
       <c r="I13" t="str">
-        <v>Paypal</v>
+        <v>Card</v>
       </c>
       <c r="J13">
-        <v>69.13</v>
+        <v>56</v>
       </c>
       <c r="K13" t="str">
         <v/>
@@ -2406,7 +2172,7 @@
         <v/>
       </c>
       <c r="N13">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="O13" t="str">
         <v/>
@@ -2420,34 +2186,34 @@
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>2026-07-02</v>
+        <v>2026-07-14</v>
       </c>
       <c r="B14" t="str">
-        <v>BM-5049</v>
+        <v>BM-5061</v>
       </c>
       <c r="C14" t="str">
-        <v>IPH-128GB-BLA</v>
+        <v>SAM-128GB-WHI</v>
       </c>
       <c r="D14" t="str">
-        <v>350100000388031</v>
+        <v>350100000483059</v>
       </c>
       <c r="E14" t="str">
-        <v>NORTHSIDE STOCK</v>
+        <v>MOBILE WHOLESALE LTD</v>
       </c>
       <c r="F14">
         <v>1</v>
       </c>
       <c r="G14">
-        <v>232.81</v>
+        <v>250.16</v>
       </c>
       <c r="H14">
-        <v>312.96</v>
+        <v>352.23</v>
       </c>
       <c r="I14" t="str">
-        <v>Klarna</v>
+        <v>Paypal</v>
       </c>
       <c r="J14">
-        <v>80.14999999999998</v>
+        <v>102.07000000000002</v>
       </c>
       <c r="K14" t="str">
         <v/>
@@ -2459,7 +2225,7 @@
         <v/>
       </c>
       <c r="N14">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="O14" t="str">
         <v/>
@@ -2473,34 +2239,34 @@
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>2026-07-06</v>
+        <v>2026-07-19</v>
       </c>
       <c r="B15" t="str">
-        <v>BM-5053</v>
+        <v>BM-5066</v>
       </c>
       <c r="C15" t="str">
-        <v>SAM-128GB-STA</v>
+        <v>IPH-128GB-BLA</v>
       </c>
       <c r="D15" t="str">
-        <v>350100000419707</v>
+        <v>350100000522654</v>
       </c>
       <c r="E15" t="str">
-        <v>MOBILE WHOLESALE LTD</v>
+        <v>CELLHUB TRADING</v>
       </c>
       <c r="F15">
         <v>1</v>
       </c>
       <c r="G15">
-        <v>243.53</v>
+        <v>337.53</v>
       </c>
       <c r="H15">
-        <v>355.54</v>
+        <v>453.07</v>
       </c>
       <c r="I15" t="str">
-        <v>Card</v>
+        <v>Paypal</v>
       </c>
       <c r="J15">
-        <v>112.01000000000002</v>
+        <v>115.54000000000002</v>
       </c>
       <c r="K15" t="str">
         <v/>
@@ -2512,7 +2278,7 @@
         <v/>
       </c>
       <c r="N15">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="O15" t="str">
         <v/>
@@ -2526,16 +2292,16 @@
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>2026-07-10</v>
+        <v>2026-07-24</v>
       </c>
       <c r="B16" t="str">
-        <v>BM-5057</v>
+        <v>BM-5071</v>
       </c>
       <c r="C16" t="str">
-        <v>IPH-128GB-BLA</v>
+        <v>GOO-128GB-BLU</v>
       </c>
       <c r="D16" t="str">
-        <v>350100000451383</v>
+        <v>350100000562249</v>
       </c>
       <c r="E16" t="str">
         <v>PHONEBOX DIRECT</v>
@@ -2544,16 +2310,16 @@
         <v>1</v>
       </c>
       <c r="G16">
-        <v>218.51</v>
+        <v>264.82</v>
       </c>
       <c r="H16">
-        <v>289.95</v>
+        <v>382.77</v>
       </c>
       <c r="I16" t="str">
-        <v>Paypal</v>
+        <v>Klarna</v>
       </c>
       <c r="J16">
-        <v>71.44</v>
+        <v>117.94999999999999</v>
       </c>
       <c r="K16" t="str">
         <v/>
@@ -2579,16 +2345,16 @@
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v>2026-07-14</v>
+        <v>2026-07-05</v>
       </c>
       <c r="B17" t="str">
-        <v>BM-5061</v>
+        <v>BM-5076</v>
       </c>
       <c r="C17" t="str">
-        <v>SAM-128GB-WHI</v>
+        <v>IPH-256GB-STA</v>
       </c>
       <c r="D17" t="str">
-        <v>350100000483059</v>
+        <v>350100000601844</v>
       </c>
       <c r="E17" t="str">
         <v>MOBILE WHOLESALE LTD</v>
@@ -2597,16 +2363,16 @@
         <v>1</v>
       </c>
       <c r="G17">
-        <v>250.16</v>
+        <v>476.5</v>
       </c>
       <c r="H17">
-        <v>347.92</v>
+        <v>605.3</v>
       </c>
       <c r="I17" t="str">
-        <v>Klarna</v>
+        <v>Paypal</v>
       </c>
       <c r="J17">
-        <v>97.76000000000002</v>
+        <v>128.79999999999995</v>
       </c>
       <c r="K17" t="str">
         <v/>
@@ -2632,16 +2398,16 @@
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v>2026-07-18</v>
+        <v>2026-07-10</v>
       </c>
       <c r="B18" t="str">
-        <v>BM-5065</v>
+        <v>BM-5081</v>
       </c>
       <c r="C18" t="str">
-        <v>IPH-128GB-WHI</v>
+        <v>IPH-128GB-PUR</v>
       </c>
       <c r="D18" t="str">
-        <v>350100000514735</v>
+        <v>350100000641439</v>
       </c>
       <c r="E18" t="str">
         <v>PHONEBOX DIRECT</v>
@@ -2650,16 +2416,16 @@
         <v>1</v>
       </c>
       <c r="G18">
-        <v>222.24</v>
+        <v>231.07</v>
       </c>
       <c r="H18">
-        <v>312.92</v>
+        <v>317.79</v>
       </c>
       <c r="I18" t="str">
-        <v>Paypal</v>
+        <v>Klarna</v>
       </c>
       <c r="J18">
-        <v>90.68</v>
+        <v>86.72000000000003</v>
       </c>
       <c r="K18" t="str">
         <v/>
@@ -2685,16 +2451,16 @@
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v>2026-07-22</v>
+        <v>2026-07-15</v>
       </c>
       <c r="B19" t="str">
-        <v>BM-5069</v>
+        <v>BM-5086</v>
       </c>
       <c r="C19" t="str">
-        <v>SAM-128GB-BLU</v>
+        <v>SAM-256GB-GRA</v>
       </c>
       <c r="D19" t="str">
-        <v>350100000546411</v>
+        <v>350100000681034</v>
       </c>
       <c r="E19" t="str">
         <v>MOBILE WHOLESALE LTD</v>
@@ -2703,16 +2469,16 @@
         <v>1</v>
       </c>
       <c r="G19">
-        <v>263.11</v>
+        <v>413.46</v>
       </c>
       <c r="H19">
-        <v>367.36</v>
+        <v>533.81</v>
       </c>
       <c r="I19" t="str">
-        <v>Klarna</v>
+        <v>Card</v>
       </c>
       <c r="J19">
-        <v>104.25</v>
+        <v>120.34999999999997</v>
       </c>
       <c r="K19" t="str">
         <v/>
@@ -2738,16 +2504,16 @@
     </row>
     <row r="20">
       <c r="A20" t="str">
-        <v>2026-07-02</v>
+        <v>2026-07-20</v>
       </c>
       <c r="B20" t="str">
-        <v>BM-5073</v>
+        <v>BM-5091</v>
       </c>
       <c r="C20" t="str">
-        <v>IPH-128GB-MID</v>
+        <v>IPH-256GB-GRA</v>
       </c>
       <c r="D20" t="str">
-        <v>350100000578087</v>
+        <v>350100007847729</v>
       </c>
       <c r="E20" t="str">
         <v>NORTHSIDE STOCK</v>
@@ -2756,16 +2522,16 @@
         <v>1</v>
       </c>
       <c r="G20">
-        <v>222.91</v>
+        <v>530.25</v>
       </c>
       <c r="H20">
-        <v>318.37</v>
+        <v>746.88</v>
       </c>
       <c r="I20" t="str">
-        <v>Card</v>
+        <v>Klarna</v>
       </c>
       <c r="J20">
-        <v>95.46000000000001</v>
+        <v>216.63</v>
       </c>
       <c r="K20" t="str">
         <v/>
@@ -2791,16 +2557,16 @@
     </row>
     <row r="21">
       <c r="A21" t="str">
-        <v>2026-07-06</v>
+        <v>2026-07-01</v>
       </c>
       <c r="B21" t="str">
-        <v>BM-5077</v>
+        <v>BM-5096</v>
       </c>
       <c r="C21" t="str">
-        <v>SAM-128GB-WHI</v>
+        <v>IPH-128GB-GRA</v>
       </c>
       <c r="D21" t="str">
-        <v>350100000609763</v>
+        <v>350100007887324</v>
       </c>
       <c r="E21" t="str">
         <v>PHONEBOX DIRECT</v>
@@ -2809,16 +2575,16 @@
         <v>1</v>
       </c>
       <c r="G21">
-        <v>257.31</v>
+        <v>223.04</v>
       </c>
       <c r="H21">
-        <v>363.2</v>
+        <v>298.35</v>
       </c>
       <c r="I21" t="str">
         <v>Klarna</v>
       </c>
       <c r="J21">
-        <v>105.88999999999999</v>
+        <v>75.31000000000003</v>
       </c>
       <c r="K21" t="str">
         <v/>
@@ -2842,281 +2608,16 @@
         <v/>
       </c>
     </row>
-    <row r="22">
-      <c r="A22" t="str">
-        <v>2026-07-10</v>
-      </c>
-      <c r="B22" t="str">
-        <v>BM-5081</v>
-      </c>
-      <c r="C22" t="str">
-        <v>IPH-128GB-PUR</v>
-      </c>
-      <c r="D22" t="str">
-        <v>350100000641439</v>
-      </c>
-      <c r="E22" t="str">
-        <v>PHONEBOX DIRECT</v>
-      </c>
-      <c r="F22">
-        <v>1</v>
-      </c>
-      <c r="G22">
-        <v>231.07</v>
-      </c>
-      <c r="H22">
-        <v>293.53</v>
-      </c>
-      <c r="I22" t="str">
-        <v>Paypal</v>
-      </c>
-      <c r="J22">
-        <v>62.45999999999998</v>
-      </c>
-      <c r="K22" t="str">
-        <v/>
-      </c>
-      <c r="L22" t="str">
-        <v/>
-      </c>
-      <c r="M22" t="str">
-        <v/>
-      </c>
-      <c r="N22">
-        <v>8</v>
-      </c>
-      <c r="O22" t="str">
-        <v/>
-      </c>
-      <c r="P22" t="str">
-        <v/>
-      </c>
-      <c r="Q22" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="str">
-        <v>2026-07-14</v>
-      </c>
-      <c r="B23" t="str">
-        <v>BM-5085</v>
-      </c>
-      <c r="C23" t="str">
-        <v>SAM-128GB-GRA</v>
-      </c>
-      <c r="D23" t="str">
-        <v>350100000673115</v>
-      </c>
-      <c r="E23" t="str">
-        <v>NORTHSIDE STOCK</v>
-      </c>
-      <c r="F23">
-        <v>1</v>
-      </c>
-      <c r="G23">
-        <v>246.21</v>
-      </c>
-      <c r="H23">
-        <v>352.53</v>
-      </c>
-      <c r="I23" t="str">
-        <v>Klarna</v>
-      </c>
-      <c r="J23">
-        <v>106.31999999999996</v>
-      </c>
-      <c r="K23" t="str">
-        <v/>
-      </c>
-      <c r="L23" t="str">
-        <v/>
-      </c>
-      <c r="M23" t="str">
-        <v/>
-      </c>
-      <c r="N23">
-        <v>6.3</v>
-      </c>
-      <c r="O23" t="str">
-        <v/>
-      </c>
-      <c r="P23" t="str">
-        <v/>
-      </c>
-      <c r="Q23" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="str">
-        <v>2026-07-18</v>
-      </c>
-      <c r="B24" t="str">
-        <v>BM-5089</v>
-      </c>
-      <c r="C24" t="str">
-        <v>IPH-128GB-MID</v>
-      </c>
-      <c r="D24" t="str">
-        <v>350100000704791</v>
-      </c>
-      <c r="E24" t="str">
-        <v>MOBILE WHOLESALE LTD</v>
-      </c>
-      <c r="F24">
-        <v>1</v>
-      </c>
-      <c r="G24">
-        <v>227.85</v>
-      </c>
-      <c r="H24">
-        <v>336.95</v>
-      </c>
-      <c r="I24" t="str">
-        <v>Klarna</v>
-      </c>
-      <c r="J24">
-        <v>109.1</v>
-      </c>
-      <c r="K24" t="str">
-        <v/>
-      </c>
-      <c r="L24" t="str">
-        <v/>
-      </c>
-      <c r="M24" t="str">
-        <v/>
-      </c>
-      <c r="N24">
-        <v>6.3</v>
-      </c>
-      <c r="O24" t="str">
-        <v/>
-      </c>
-      <c r="P24" t="str">
-        <v/>
-      </c>
-      <c r="Q24" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="str">
-        <v>2026-07-22</v>
-      </c>
-      <c r="B25" t="str">
-        <v>BM-5093</v>
-      </c>
-      <c r="C25" t="str">
-        <v>SAM-128GB-MID</v>
-      </c>
-      <c r="D25" t="str">
-        <v>350100007863567</v>
-      </c>
-      <c r="E25" t="str">
-        <v>NORTHSIDE STOCK</v>
-      </c>
-      <c r="F25">
-        <v>1</v>
-      </c>
-      <c r="G25">
-        <v>242</v>
-      </c>
-      <c r="H25">
-        <v>356.32</v>
-      </c>
-      <c r="I25" t="str">
-        <v>Card</v>
-      </c>
-      <c r="J25">
-        <v>114.32</v>
-      </c>
-      <c r="K25" t="str">
-        <v/>
-      </c>
-      <c r="L25" t="str">
-        <v/>
-      </c>
-      <c r="M25" t="str">
-        <v/>
-      </c>
-      <c r="N25">
-        <v>8</v>
-      </c>
-      <c r="O25" t="str">
-        <v/>
-      </c>
-      <c r="P25" t="str">
-        <v/>
-      </c>
-      <c r="Q25" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="str">
-        <v>2026-07-02</v>
-      </c>
-      <c r="B26" t="str">
-        <v>BM-5097</v>
-      </c>
-      <c r="C26" t="str">
-        <v>IPH-128GB-GRA</v>
-      </c>
-      <c r="D26" t="str">
-        <v>350100007895243</v>
-      </c>
-      <c r="E26" t="str">
-        <v>PHONEBOX DIRECT</v>
-      </c>
-      <c r="F26">
-        <v>1</v>
-      </c>
-      <c r="G26">
-        <v>223.04</v>
-      </c>
-      <c r="H26">
-        <v>314.16</v>
-      </c>
-      <c r="I26" t="str">
-        <v>Klarna</v>
-      </c>
-      <c r="J26">
-        <v>91.12000000000003</v>
-      </c>
-      <c r="K26" t="str">
-        <v/>
-      </c>
-      <c r="L26" t="str">
-        <v/>
-      </c>
-      <c r="M26" t="str">
-        <v/>
-      </c>
-      <c r="N26">
-        <v>8</v>
-      </c>
-      <c r="O26" t="str">
-        <v/>
-      </c>
-      <c r="P26" t="str">
-        <v/>
-      </c>
-      <c r="Q26" t="str">
-        <v/>
-      </c>
-    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:Q26"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:Q21"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:S26"/>
+  <dimension ref="A1:S21"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -3238,31 +2739,31 @@
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>2026-07-07</v>
+        <v>2026-07-08</v>
       </c>
       <c r="B3" t="str">
-        <v>EBA-5006</v>
+        <v>EBA-5007</v>
       </c>
       <c r="C3" t="str">
-        <v>SAM-256GB-WHI</v>
+        <v>GOO-128GB-WHI</v>
       </c>
       <c r="D3" t="str">
-        <v>350100000047514</v>
+        <v>350100000055433</v>
       </c>
       <c r="E3" t="str">
-        <v>PHONEBOX DIRECT</v>
+        <v>CELLHUB TRADING</v>
       </c>
       <c r="F3">
         <v>1</v>
       </c>
       <c r="G3">
-        <v>446.53</v>
+        <v>260.29</v>
       </c>
       <c r="H3">
-        <v>643.55</v>
+        <v>371.44</v>
       </c>
       <c r="I3">
-        <v>197.01999999999998</v>
+        <v>111.14999999999998</v>
       </c>
       <c r="J3" t="str">
         <v/>
@@ -3297,31 +2798,31 @@
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>2026-07-11</v>
+        <v>2026-07-13</v>
       </c>
       <c r="B4" t="str">
-        <v>EBA-5010</v>
+        <v>EBA-5012</v>
       </c>
       <c r="C4" t="str">
-        <v>IPH-128GB-GRE</v>
+        <v>SAM-128GB-BLU</v>
       </c>
       <c r="D4" t="str">
-        <v>350100000079190</v>
+        <v>350100000102947</v>
       </c>
       <c r="E4" t="str">
-        <v>PHONEBOX DIRECT</v>
+        <v>MOBILE WHOLESALE LTD</v>
       </c>
       <c r="F4">
         <v>1</v>
       </c>
       <c r="G4">
-        <v>311.8</v>
+        <v>230.57</v>
       </c>
       <c r="H4">
-        <v>466.51</v>
+        <v>319.34</v>
       </c>
       <c r="I4">
-        <v>154.70999999999998</v>
+        <v>88.76999999999998</v>
       </c>
       <c r="J4" t="str">
         <v/>
@@ -3342,7 +2843,7 @@
         <v/>
       </c>
       <c r="P4">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="Q4" t="str">
         <v/>
@@ -3356,31 +2857,31 @@
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>2026-07-15</v>
+        <v>2026-07-18</v>
       </c>
       <c r="B5" t="str">
-        <v>EBA-5014</v>
+        <v>EBA-5017</v>
       </c>
       <c r="C5" t="str">
-        <v>SAM-256GB-WHI</v>
+        <v>IPH-128GB-GRA</v>
       </c>
       <c r="D5" t="str">
-        <v>350100000110866</v>
+        <v>350100000134623</v>
       </c>
       <c r="E5" t="str">
-        <v>PHONEBOX DIRECT</v>
+        <v>CELLHUB TRADING</v>
       </c>
       <c r="F5">
         <v>1</v>
       </c>
       <c r="G5">
-        <v>450.57</v>
+        <v>219.35</v>
       </c>
       <c r="H5">
-        <v>611.06</v>
+        <v>322.18</v>
       </c>
       <c r="I5">
-        <v>160.48999999999995</v>
+        <v>102.83000000000001</v>
       </c>
       <c r="J5" t="str">
         <v/>
@@ -3401,7 +2902,7 @@
         <v/>
       </c>
       <c r="P5">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="Q5" t="str">
         <v/>
@@ -3415,16 +2916,16 @@
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>2026-07-19</v>
+        <v>2026-07-23</v>
       </c>
       <c r="B6" t="str">
-        <v>EBA-5018</v>
+        <v>EBA-5022</v>
       </c>
       <c r="C6" t="str">
-        <v>IPH-128GB-BLU</v>
+        <v>SAM-256GB-MID</v>
       </c>
       <c r="D6" t="str">
-        <v>350100000142542</v>
+        <v>350100000174218</v>
       </c>
       <c r="E6" t="str">
         <v>CELLHUB TRADING</v>
@@ -3433,13 +2934,13 @@
         <v>1</v>
       </c>
       <c r="G6">
-        <v>316.37</v>
+        <v>449.53</v>
       </c>
       <c r="H6">
-        <v>464.68</v>
+        <v>632.67</v>
       </c>
       <c r="I6">
-        <v>148.31</v>
+        <v>183.14</v>
       </c>
       <c r="J6" t="str">
         <v/>
@@ -3460,7 +2961,7 @@
         <v/>
       </c>
       <c r="P6">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="Q6" t="str">
         <v/>
@@ -3474,31 +2975,31 @@
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>2026-07-23</v>
+        <v>2026-07-04</v>
       </c>
       <c r="B7" t="str">
-        <v>EBA-5022</v>
+        <v>EBA-5027</v>
       </c>
       <c r="C7" t="str">
-        <v>SAM-256GB-MID</v>
+        <v>IPH-256GB-MID</v>
       </c>
       <c r="D7" t="str">
-        <v>350100000174218</v>
+        <v>350100000213813</v>
       </c>
       <c r="E7" t="str">
-        <v>CELLHUB TRADING</v>
+        <v>PHONEBOX DIRECT</v>
       </c>
       <c r="F7">
         <v>1</v>
       </c>
       <c r="G7">
-        <v>449.53</v>
+        <v>499.91</v>
       </c>
       <c r="H7">
-        <v>590.13</v>
+        <v>726.64</v>
       </c>
       <c r="I7">
-        <v>140.60000000000002</v>
+        <v>226.72999999999996</v>
       </c>
       <c r="J7" t="str">
         <v/>
@@ -3533,16 +3034,16 @@
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>2026-07-03</v>
+        <v>2026-07-09</v>
       </c>
       <c r="B8" t="str">
-        <v>EBA-5026</v>
+        <v>EBA-5032</v>
       </c>
       <c r="C8" t="str">
-        <v>IPH-128GB-PUR</v>
+        <v>IPH-64GB-GRE</v>
       </c>
       <c r="D8" t="str">
-        <v>350100000205894</v>
+        <v>350100000253408</v>
       </c>
       <c r="E8" t="str">
         <v>PHONEBOX DIRECT</v>
@@ -3551,13 +3052,13 @@
         <v>1</v>
       </c>
       <c r="G8">
-        <v>325.88</v>
+        <v>196.32</v>
       </c>
       <c r="H8">
-        <v>461.56</v>
+        <v>281.67</v>
       </c>
       <c r="I8">
-        <v>135.68</v>
+        <v>85.35000000000002</v>
       </c>
       <c r="J8" t="str">
         <v/>
@@ -3592,16 +3093,16 @@
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>2026-07-07</v>
+        <v>2026-07-14</v>
       </c>
       <c r="B9" t="str">
-        <v>EBA-5030</v>
+        <v>EBA-5037</v>
       </c>
       <c r="C9" t="str">
-        <v>SAM-256GB-GRA</v>
+        <v>SAM-128GB-GRE</v>
       </c>
       <c r="D9" t="str">
-        <v>350100000237570</v>
+        <v>350100000293003</v>
       </c>
       <c r="E9" t="str">
         <v>MOBILE WHOLESALE LTD</v>
@@ -3610,13 +3111,13 @@
         <v>1</v>
       </c>
       <c r="G9">
-        <v>418.34</v>
+        <v>262.94</v>
       </c>
       <c r="H9">
-        <v>567.87</v>
+        <v>393.16</v>
       </c>
       <c r="I9">
-        <v>149.53000000000003</v>
+        <v>130.22000000000003</v>
       </c>
       <c r="J9" t="str">
         <v/>
@@ -3651,31 +3152,31 @@
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>2026-07-11</v>
+        <v>2026-07-19</v>
       </c>
       <c r="B10" t="str">
-        <v>EBA-5034</v>
+        <v>EBA-5042</v>
       </c>
       <c r="C10" t="str">
-        <v>IPH-128GB-GRE</v>
+        <v>IPH-128GB-WHI</v>
       </c>
       <c r="D10" t="str">
-        <v>350100000269246</v>
+        <v>350100000332598</v>
       </c>
       <c r="E10" t="str">
-        <v>CELLHUB TRADING</v>
+        <v>NORTHSIDE STOCK</v>
       </c>
       <c r="F10">
         <v>1</v>
       </c>
       <c r="G10">
-        <v>305.4</v>
+        <v>334.64</v>
       </c>
       <c r="H10">
-        <v>438.18</v>
+        <v>432.05</v>
       </c>
       <c r="I10">
-        <v>132.78000000000003</v>
+        <v>97.41000000000003</v>
       </c>
       <c r="J10" t="str">
         <v/>
@@ -3696,7 +3197,7 @@
         <v/>
       </c>
       <c r="P10">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="Q10" t="str">
         <v/>
@@ -3710,31 +3211,31 @@
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>2026-07-15</v>
+        <v>2026-07-24</v>
       </c>
       <c r="B11" t="str">
-        <v>EBA-5038</v>
+        <v>EBA-5047</v>
       </c>
       <c r="C11" t="str">
-        <v>SAM-256GB-MID</v>
+        <v>GOO-128GB-GRA</v>
       </c>
       <c r="D11" t="str">
-        <v>350100000300922</v>
+        <v>350100000372193</v>
       </c>
       <c r="E11" t="str">
-        <v>NORTHSIDE STOCK</v>
+        <v>CELLHUB TRADING</v>
       </c>
       <c r="F11">
         <v>1</v>
       </c>
       <c r="G11">
-        <v>422.16</v>
+        <v>256.93</v>
       </c>
       <c r="H11">
-        <v>623.08</v>
+        <v>344.13</v>
       </c>
       <c r="I11">
-        <v>200.92000000000002</v>
+        <v>87.19999999999999</v>
       </c>
       <c r="J11" t="str">
         <v/>
@@ -3769,31 +3270,31 @@
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>2026-07-19</v>
+        <v>2026-07-05</v>
       </c>
       <c r="B12" t="str">
-        <v>EBA-5042</v>
+        <v>EBA-5052</v>
       </c>
       <c r="C12" t="str">
-        <v>IPH-128GB-WHI</v>
+        <v>IPH-256GB-PUR</v>
       </c>
       <c r="D12" t="str">
-        <v>350100000332598</v>
+        <v>350100000411788</v>
       </c>
       <c r="E12" t="str">
-        <v>NORTHSIDE STOCK</v>
+        <v>MOBILE WHOLESALE LTD</v>
       </c>
       <c r="F12">
         <v>1</v>
       </c>
       <c r="G12">
-        <v>334.64</v>
+        <v>497.17</v>
       </c>
       <c r="H12">
-        <v>424.77</v>
+        <v>654.36</v>
       </c>
       <c r="I12">
-        <v>90.13</v>
+        <v>157.19</v>
       </c>
       <c r="J12" t="str">
         <v/>
@@ -3814,7 +3315,7 @@
         <v/>
       </c>
       <c r="P12">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="Q12" t="str">
         <v/>
@@ -3828,31 +3329,31 @@
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>2026-07-23</v>
+        <v>2026-07-10</v>
       </c>
       <c r="B13" t="str">
-        <v>EBA-5046</v>
+        <v>EBA-5057</v>
       </c>
       <c r="C13" t="str">
-        <v>SAM-256GB-PUR</v>
+        <v>IPH-128GB-BLA</v>
       </c>
       <c r="D13" t="str">
-        <v>350100000364274</v>
+        <v>350100000451383</v>
       </c>
       <c r="E13" t="str">
-        <v>MOBILE WHOLESALE LTD</v>
+        <v>PHONEBOX DIRECT</v>
       </c>
       <c r="F13">
         <v>1</v>
       </c>
       <c r="G13">
-        <v>453.75</v>
+        <v>218.51</v>
       </c>
       <c r="H13">
-        <v>660.67</v>
+        <v>303.91</v>
       </c>
       <c r="I13">
-        <v>206.91999999999996</v>
+        <v>85.40000000000003</v>
       </c>
       <c r="J13" t="str">
         <v/>
@@ -3873,7 +3374,7 @@
         <v/>
       </c>
       <c r="P13">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="Q13" t="str">
         <v/>
@@ -3887,31 +3388,31 @@
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>2026-07-03</v>
+        <v>2026-07-15</v>
       </c>
       <c r="B14" t="str">
-        <v>EBA-5050</v>
+        <v>EBA-5062</v>
       </c>
       <c r="C14" t="str">
-        <v>IPH-128GB-BLU</v>
+        <v>SAM-256GB-BLU</v>
       </c>
       <c r="D14" t="str">
-        <v>350100000395950</v>
+        <v>350100000490978</v>
       </c>
       <c r="E14" t="str">
-        <v>PHONEBOX DIRECT</v>
+        <v>CELLHUB TRADING</v>
       </c>
       <c r="F14">
         <v>1</v>
       </c>
       <c r="G14">
-        <v>316.67</v>
+        <v>431.55</v>
       </c>
       <c r="H14">
-        <v>424.14</v>
+        <v>555.17</v>
       </c>
       <c r="I14">
-        <v>107.46999999999997</v>
+        <v>123.61999999999995</v>
       </c>
       <c r="J14" t="str">
         <v/>
@@ -3946,31 +3447,31 @@
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>2026-07-07</v>
+        <v>2026-07-20</v>
       </c>
       <c r="B15" t="str">
-        <v>EBA-5054</v>
+        <v>EBA-5067</v>
       </c>
       <c r="C15" t="str">
-        <v>SAM-256GB-GRA</v>
+        <v>IPH-256GB-GRA</v>
       </c>
       <c r="D15" t="str">
-        <v>350100000427626</v>
+        <v>350100000530573</v>
       </c>
       <c r="E15" t="str">
-        <v>NORTHSIDE STOCK</v>
+        <v>CELLHUB TRADING</v>
       </c>
       <c r="F15">
         <v>1</v>
       </c>
       <c r="G15">
-        <v>405.86</v>
+        <v>500.16</v>
       </c>
       <c r="H15">
-        <v>602.26</v>
+        <v>745.1</v>
       </c>
       <c r="I15">
-        <v>196.39999999999998</v>
+        <v>244.94</v>
       </c>
       <c r="J15" t="str">
         <v/>
@@ -4005,31 +3506,31 @@
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>2026-07-11</v>
+        <v>2026-07-01</v>
       </c>
       <c r="B16" t="str">
-        <v>EBA-5058</v>
+        <v>EBA-5072</v>
       </c>
       <c r="C16" t="str">
-        <v>IPH-128GB-WHI</v>
+        <v>IPH-128GB-MID</v>
       </c>
       <c r="D16" t="str">
-        <v>350100000459302</v>
+        <v>350100000578087</v>
       </c>
       <c r="E16" t="str">
-        <v>PHONEBOX DIRECT</v>
+        <v>NORTHSIDE STOCK</v>
       </c>
       <c r="F16">
         <v>1</v>
       </c>
       <c r="G16">
-        <v>336.42</v>
+        <v>222.91</v>
       </c>
       <c r="H16">
-        <v>447.02</v>
+        <v>314.64</v>
       </c>
       <c r="I16">
-        <v>110.59999999999997</v>
+        <v>91.72999999999999</v>
       </c>
       <c r="J16" t="str">
         <v/>
@@ -4064,31 +3565,31 @@
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v>2026-07-15</v>
+        <v>2026-07-06</v>
       </c>
       <c r="B17" t="str">
-        <v>EBA-5062</v>
+        <v>EBA-5077</v>
       </c>
       <c r="C17" t="str">
-        <v>SAM-256GB-BLU</v>
+        <v>SAM-128GB-WHI</v>
       </c>
       <c r="D17" t="str">
-        <v>350100000490978</v>
+        <v>350100000609763</v>
       </c>
       <c r="E17" t="str">
-        <v>CELLHUB TRADING</v>
+        <v>PHONEBOX DIRECT</v>
       </c>
       <c r="F17">
         <v>1</v>
       </c>
       <c r="G17">
-        <v>431.55</v>
+        <v>257.31</v>
       </c>
       <c r="H17">
-        <v>553.53</v>
+        <v>378.96</v>
       </c>
       <c r="I17">
-        <v>121.97999999999996</v>
+        <v>121.64999999999998</v>
       </c>
       <c r="J17" t="str">
         <v/>
@@ -4123,31 +3624,31 @@
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v>2026-07-19</v>
+        <v>2026-07-11</v>
       </c>
       <c r="B18" t="str">
-        <v>EBA-5066</v>
+        <v>EBA-5082</v>
       </c>
       <c r="C18" t="str">
-        <v>IPH-128GB-BLA</v>
+        <v>IPH-128GB-MID</v>
       </c>
       <c r="D18" t="str">
-        <v>350100000522654</v>
+        <v>350100000649358</v>
       </c>
       <c r="E18" t="str">
-        <v>CELLHUB TRADING</v>
+        <v>PHONEBOX DIRECT</v>
       </c>
       <c r="F18">
         <v>1</v>
       </c>
       <c r="G18">
-        <v>337.53</v>
+        <v>315.22</v>
       </c>
       <c r="H18">
-        <v>434.22</v>
+        <v>397.26</v>
       </c>
       <c r="I18">
-        <v>96.69000000000005</v>
+        <v>82.03999999999996</v>
       </c>
       <c r="J18" t="str">
         <v/>
@@ -4182,31 +3683,31 @@
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v>2026-07-23</v>
+        <v>2026-07-16</v>
       </c>
       <c r="B19" t="str">
-        <v>EBA-5070</v>
+        <v>EBA-5087</v>
       </c>
       <c r="C19" t="str">
-        <v>SAM-256GB-GRA</v>
+        <v>GOO-128GB-STA</v>
       </c>
       <c r="D19" t="str">
-        <v>350100000554330</v>
+        <v>350100000688953</v>
       </c>
       <c r="E19" t="str">
-        <v>CELLHUB TRADING</v>
+        <v>PHONEBOX DIRECT</v>
       </c>
       <c r="F19">
         <v>1</v>
       </c>
       <c r="G19">
-        <v>451.39</v>
+        <v>275.49</v>
       </c>
       <c r="H19">
-        <v>605.91</v>
+        <v>405.63</v>
       </c>
       <c r="I19">
-        <v>154.51999999999998</v>
+        <v>130.14</v>
       </c>
       <c r="J19" t="str">
         <v/>
@@ -4227,7 +3728,7 @@
         <v/>
       </c>
       <c r="P19">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="Q19" t="str">
         <v/>
@@ -4241,31 +3742,31 @@
     </row>
     <row r="20">
       <c r="A20" t="str">
-        <v>2026-07-03</v>
+        <v>2026-07-21</v>
       </c>
       <c r="B20" t="str">
-        <v>EBA-5074</v>
+        <v>EBA-5092</v>
       </c>
       <c r="C20" t="str">
-        <v>IPH-128GB-PUR</v>
+        <v>IPH-256GB-GRA</v>
       </c>
       <c r="D20" t="str">
-        <v>350100000586006</v>
+        <v>350100007855648</v>
       </c>
       <c r="E20" t="str">
-        <v>NORTHSIDE STOCK</v>
+        <v>PHONEBOX DIRECT</v>
       </c>
       <c r="F20">
         <v>1</v>
       </c>
       <c r="G20">
-        <v>334.66</v>
+        <v>462.92</v>
       </c>
       <c r="H20">
-        <v>451.26</v>
+        <v>686.89</v>
       </c>
       <c r="I20">
-        <v>116.59999999999997</v>
+        <v>223.96999999999997</v>
       </c>
       <c r="J20" t="str">
         <v/>
@@ -4300,16 +3801,16 @@
     </row>
     <row r="21">
       <c r="A21" t="str">
-        <v>2026-07-07</v>
+        <v>2026-07-02</v>
       </c>
       <c r="B21" t="str">
-        <v>EBA-5078</v>
+        <v>EBA-5097</v>
       </c>
       <c r="C21" t="str">
-        <v>SAM-256GB-GRE</v>
+        <v>IPH-128GB-GRA</v>
       </c>
       <c r="D21" t="str">
-        <v>350100000617682</v>
+        <v>350100007895243</v>
       </c>
       <c r="E21" t="str">
         <v>PHONEBOX DIRECT</v>
@@ -4318,13 +3819,13 @@
         <v>1</v>
       </c>
       <c r="G21">
-        <v>422.7</v>
+        <v>223.04</v>
       </c>
       <c r="H21">
-        <v>579.8</v>
+        <v>305.42</v>
       </c>
       <c r="I21">
-        <v>157.09999999999997</v>
+        <v>82.38000000000002</v>
       </c>
       <c r="J21" t="str">
         <v/>
@@ -4345,7 +3846,7 @@
         <v/>
       </c>
       <c r="P21">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="Q21" t="str">
         <v/>
@@ -4354,314 +3855,19 @@
         <v/>
       </c>
       <c r="S21" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="str">
-        <v>2026-07-11</v>
-      </c>
-      <c r="B22" t="str">
-        <v>EBA-5082</v>
-      </c>
-      <c r="C22" t="str">
-        <v>IPH-128GB-MID</v>
-      </c>
-      <c r="D22" t="str">
-        <v>350100000649358</v>
-      </c>
-      <c r="E22" t="str">
-        <v>PHONEBOX DIRECT</v>
-      </c>
-      <c r="F22">
-        <v>1</v>
-      </c>
-      <c r="G22">
-        <v>315.22</v>
-      </c>
-      <c r="H22">
-        <v>464.25</v>
-      </c>
-      <c r="I22">
-        <v>149.02999999999997</v>
-      </c>
-      <c r="J22" t="str">
-        <v/>
-      </c>
-      <c r="K22" t="str">
-        <v/>
-      </c>
-      <c r="L22" t="str">
-        <v/>
-      </c>
-      <c r="M22" t="str">
-        <v/>
-      </c>
-      <c r="N22" t="str">
-        <v/>
-      </c>
-      <c r="O22" t="str">
-        <v/>
-      </c>
-      <c r="P22">
-        <v>8</v>
-      </c>
-      <c r="Q22" t="str">
-        <v/>
-      </c>
-      <c r="R22" t="str">
-        <v/>
-      </c>
-      <c r="S22" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="str">
-        <v>2026-07-15</v>
-      </c>
-      <c r="B23" t="str">
-        <v>EBA-5086</v>
-      </c>
-      <c r="C23" t="str">
-        <v>SAM-256GB-GRA</v>
-      </c>
-      <c r="D23" t="str">
-        <v>350100000681034</v>
-      </c>
-      <c r="E23" t="str">
-        <v>MOBILE WHOLESALE LTD</v>
-      </c>
-      <c r="F23">
-        <v>1</v>
-      </c>
-      <c r="G23">
-        <v>413.46</v>
-      </c>
-      <c r="H23">
-        <v>568.64</v>
-      </c>
-      <c r="I23">
-        <v>155.18</v>
-      </c>
-      <c r="J23" t="str">
-        <v/>
-      </c>
-      <c r="K23" t="str">
-        <v/>
-      </c>
-      <c r="L23" t="str">
-        <v/>
-      </c>
-      <c r="M23" t="str">
-        <v/>
-      </c>
-      <c r="N23" t="str">
-        <v/>
-      </c>
-      <c r="O23" t="str">
-        <v/>
-      </c>
-      <c r="P23">
-        <v>8</v>
-      </c>
-      <c r="Q23" t="str">
-        <v/>
-      </c>
-      <c r="R23" t="str">
-        <v/>
-      </c>
-      <c r="S23" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="str">
-        <v>2026-07-19</v>
-      </c>
-      <c r="B24" t="str">
-        <v>EBA-5090</v>
-      </c>
-      <c r="C24" t="str">
-        <v>IPH-128GB-GRA</v>
-      </c>
-      <c r="D24" t="str">
-        <v>350100007839810</v>
-      </c>
-      <c r="E24" t="str">
-        <v>PHONEBOX DIRECT</v>
-      </c>
-      <c r="F24">
-        <v>1</v>
-      </c>
-      <c r="G24">
-        <v>335.04</v>
-      </c>
-      <c r="H24">
-        <v>490.45</v>
-      </c>
-      <c r="I24">
-        <v>155.40999999999997</v>
-      </c>
-      <c r="J24" t="str">
-        <v/>
-      </c>
-      <c r="K24" t="str">
-        <v/>
-      </c>
-      <c r="L24" t="str">
-        <v/>
-      </c>
-      <c r="M24" t="str">
-        <v/>
-      </c>
-      <c r="N24" t="str">
-        <v/>
-      </c>
-      <c r="O24" t="str">
-        <v/>
-      </c>
-      <c r="P24">
-        <v>8</v>
-      </c>
-      <c r="Q24" t="str">
-        <v/>
-      </c>
-      <c r="R24" t="str">
-        <v/>
-      </c>
-      <c r="S24" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="str">
-        <v>2026-07-23</v>
-      </c>
-      <c r="B25" t="str">
-        <v>EBA-5094</v>
-      </c>
-      <c r="C25" t="str">
-        <v>SAM-256GB-PUR</v>
-      </c>
-      <c r="D25" t="str">
-        <v>350100007871486</v>
-      </c>
-      <c r="E25" t="str">
-        <v>MOBILE WHOLESALE LTD</v>
-      </c>
-      <c r="F25">
-        <v>1</v>
-      </c>
-      <c r="G25">
-        <v>417.16</v>
-      </c>
-      <c r="H25">
-        <v>583.93</v>
-      </c>
-      <c r="I25">
-        <v>166.76999999999992</v>
-      </c>
-      <c r="J25" t="str">
-        <v/>
-      </c>
-      <c r="K25" t="str">
-        <v/>
-      </c>
-      <c r="L25" t="str">
-        <v/>
-      </c>
-      <c r="M25" t="str">
-        <v/>
-      </c>
-      <c r="N25" t="str">
-        <v/>
-      </c>
-      <c r="O25" t="str">
-        <v/>
-      </c>
-      <c r="P25">
-        <v>8</v>
-      </c>
-      <c r="Q25" t="str">
-        <v/>
-      </c>
-      <c r="R25" t="str">
-        <v/>
-      </c>
-      <c r="S25" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="str">
-        <v>2026-07-03</v>
-      </c>
-      <c r="B26" t="str">
-        <v>EBA-5098</v>
-      </c>
-      <c r="C26" t="str">
-        <v>IPH-128GB-BLA</v>
-      </c>
-      <c r="D26" t="str">
-        <v>350100007903162</v>
-      </c>
-      <c r="E26" t="str">
-        <v>CELLHUB TRADING</v>
-      </c>
-      <c r="F26">
-        <v>1</v>
-      </c>
-      <c r="G26">
-        <v>327.58</v>
-      </c>
-      <c r="H26">
-        <v>486.07</v>
-      </c>
-      <c r="I26">
-        <v>158.49</v>
-      </c>
-      <c r="J26" t="str">
-        <v/>
-      </c>
-      <c r="K26" t="str">
-        <v/>
-      </c>
-      <c r="L26" t="str">
-        <v/>
-      </c>
-      <c r="M26" t="str">
-        <v/>
-      </c>
-      <c r="N26" t="str">
-        <v/>
-      </c>
-      <c r="O26" t="str">
-        <v/>
-      </c>
-      <c r="P26">
-        <v>8</v>
-      </c>
-      <c r="Q26" t="str">
-        <v/>
-      </c>
-      <c r="R26" t="str">
-        <v/>
-      </c>
-      <c r="S26" t="str">
         <v/>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:S26"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:S21"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:O26"/>
+  <dimension ref="A1:O21"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -4759,1135 +3965,2150 @@
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>2026-07-08</v>
+        <v>2026-07-09</v>
       </c>
       <c r="B3" t="str">
-        <v>ONB-5007</v>
+        <v>ONB-5008</v>
       </c>
       <c r="C3" t="str">
-        <v>GOO-128GB-WHI</v>
+        <v>IPH-64GB-PUR</v>
       </c>
       <c r="D3" t="str">
-        <v>350100000055433</v>
+        <v>350100000063352</v>
+      </c>
+      <c r="E3" t="str">
+        <v>PHONEBOX DIRECT</v>
+      </c>
+      <c r="F3">
+        <v>196.74</v>
+      </c>
+      <c r="G3">
+        <v>251.83</v>
+      </c>
+      <c r="H3">
+        <v>55.09</v>
+      </c>
+      <c r="I3" t="str">
+        <v/>
+      </c>
+      <c r="J3" t="str">
+        <v/>
+      </c>
+      <c r="K3" t="str">
+        <v/>
+      </c>
+      <c r="L3">
+        <v>2</v>
+      </c>
+      <c r="M3" t="str">
+        <v/>
+      </c>
+      <c r="N3" t="str">
+        <v/>
+      </c>
+      <c r="O3" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="str">
+        <v>2026-07-14</v>
+      </c>
+      <c r="B4" t="str">
+        <v>ONB-5013</v>
+      </c>
+      <c r="C4" t="str">
+        <v>SAM-128GB-BLU</v>
+      </c>
+      <c r="D4" t="str">
+        <v>350100000102947</v>
+      </c>
+      <c r="E4" t="str">
+        <v>MOBILE WHOLESALE LTD</v>
+      </c>
+      <c r="F4">
+        <v>230.57</v>
+      </c>
+      <c r="G4">
+        <v>310.06</v>
+      </c>
+      <c r="H4">
+        <v>79.49000000000001</v>
+      </c>
+      <c r="I4" t="str">
+        <v/>
+      </c>
+      <c r="J4" t="str">
+        <v/>
+      </c>
+      <c r="K4" t="str">
+        <v/>
+      </c>
+      <c r="L4">
+        <v>8</v>
+      </c>
+      <c r="M4" t="str">
+        <v/>
+      </c>
+      <c r="N4" t="str">
+        <v/>
+      </c>
+      <c r="O4" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="str">
+        <v>2026-07-19</v>
+      </c>
+      <c r="B5" t="str">
+        <v>ONB-5018</v>
+      </c>
+      <c r="C5" t="str">
+        <v>IPH-128GB-BLU</v>
+      </c>
+      <c r="D5" t="str">
+        <v>350100000142542</v>
+      </c>
+      <c r="E5" t="str">
+        <v>CELLHUB TRADING</v>
+      </c>
+      <c r="F5">
+        <v>316.37</v>
+      </c>
+      <c r="G5">
+        <v>409.99</v>
+      </c>
+      <c r="H5">
+        <v>93.62</v>
+      </c>
+      <c r="I5" t="str">
+        <v/>
+      </c>
+      <c r="J5" t="str">
+        <v/>
+      </c>
+      <c r="K5" t="str">
+        <v/>
+      </c>
+      <c r="L5">
+        <v>6.3</v>
+      </c>
+      <c r="M5" t="str">
+        <v/>
+      </c>
+      <c r="N5" t="str">
+        <v/>
+      </c>
+      <c r="O5" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="str">
+        <v>2026-07-24</v>
+      </c>
+      <c r="B6" t="str">
+        <v>ONB-5023</v>
+      </c>
+      <c r="C6" t="str">
+        <v>GOO-128GB-BLA</v>
+      </c>
+      <c r="D6" t="str">
+        <v>350100000182137</v>
+      </c>
+      <c r="E6" t="str">
+        <v>CELLHUB TRADING</v>
+      </c>
+      <c r="F6">
+        <v>276.86</v>
+      </c>
+      <c r="G6">
+        <v>347.16</v>
+      </c>
+      <c r="H6">
+        <v>70.30000000000001</v>
+      </c>
+      <c r="I6" t="str">
+        <v/>
+      </c>
+      <c r="J6" t="str">
+        <v/>
+      </c>
+      <c r="K6" t="str">
+        <v/>
+      </c>
+      <c r="L6">
+        <v>2</v>
+      </c>
+      <c r="M6" t="str">
+        <v/>
+      </c>
+      <c r="N6" t="str">
+        <v/>
+      </c>
+      <c r="O6" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="str">
+        <v>2026-07-05</v>
+      </c>
+      <c r="B7" t="str">
+        <v>ONB-5028</v>
+      </c>
+      <c r="C7" t="str">
+        <v>IPH-256GB-GRA</v>
+      </c>
+      <c r="D7" t="str">
+        <v>350100000221732</v>
+      </c>
+      <c r="E7" t="str">
+        <v>PHONEBOX DIRECT</v>
+      </c>
+      <c r="F7">
+        <v>499.6</v>
+      </c>
+      <c r="G7">
+        <v>644.6</v>
+      </c>
+      <c r="H7">
+        <v>145</v>
+      </c>
+      <c r="I7" t="str">
+        <v/>
+      </c>
+      <c r="J7" t="str">
+        <v/>
+      </c>
+      <c r="K7" t="str">
+        <v/>
+      </c>
+      <c r="L7">
+        <v>8</v>
+      </c>
+      <c r="M7" t="str">
+        <v/>
+      </c>
+      <c r="N7" t="str">
+        <v/>
+      </c>
+      <c r="O7" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="str">
+        <v>2026-07-10</v>
+      </c>
+      <c r="B8" t="str">
+        <v>ONB-5033</v>
+      </c>
+      <c r="C8" t="str">
+        <v>IPH-128GB-GRE</v>
+      </c>
+      <c r="D8" t="str">
+        <v>350100000261327</v>
+      </c>
+      <c r="E8" t="str">
+        <v>CELLHUB TRADING</v>
+      </c>
+      <c r="F8">
+        <v>209.59</v>
+      </c>
+      <c r="G8">
+        <v>298.71</v>
+      </c>
+      <c r="H8">
+        <v>89.11999999999998</v>
+      </c>
+      <c r="I8" t="str">
+        <v/>
+      </c>
+      <c r="J8" t="str">
+        <v/>
+      </c>
+      <c r="K8" t="str">
+        <v/>
+      </c>
+      <c r="L8">
+        <v>8</v>
+      </c>
+      <c r="M8" t="str">
+        <v/>
+      </c>
+      <c r="N8" t="str">
+        <v/>
+      </c>
+      <c r="O8" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="str">
+        <v>2026-07-15</v>
+      </c>
+      <c r="B9" t="str">
+        <v>ONB-5038</v>
+      </c>
+      <c r="C9" t="str">
+        <v>SAM-256GB-MID</v>
+      </c>
+      <c r="D9" t="str">
+        <v>350100000300922</v>
+      </c>
+      <c r="E9" t="str">
+        <v>NORTHSIDE STOCK</v>
+      </c>
+      <c r="F9">
+        <v>422.16</v>
+      </c>
+      <c r="G9">
+        <v>534.52</v>
+      </c>
+      <c r="H9">
+        <v>112.35999999999996</v>
+      </c>
+      <c r="I9" t="str">
+        <v/>
+      </c>
+      <c r="J9" t="str">
+        <v/>
+      </c>
+      <c r="K9" t="str">
+        <v/>
+      </c>
+      <c r="L9">
+        <v>8</v>
+      </c>
+      <c r="M9" t="str">
+        <v/>
+      </c>
+      <c r="N9" t="str">
+        <v/>
+      </c>
+      <c r="O9" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="str">
+        <v>2026-07-20</v>
+      </c>
+      <c r="B10" t="str">
+        <v>ONB-5043</v>
+      </c>
+      <c r="C10" t="str">
+        <v>IPH-256GB-STA</v>
+      </c>
+      <c r="D10" t="str">
+        <v>350100000340517</v>
+      </c>
+      <c r="E10" t="str">
+        <v>NORTHSIDE STOCK</v>
+      </c>
+      <c r="F10">
+        <v>500.85</v>
+      </c>
+      <c r="G10">
+        <v>631.84</v>
+      </c>
+      <c r="H10">
+        <v>130.99</v>
+      </c>
+      <c r="I10" t="str">
+        <v/>
+      </c>
+      <c r="J10" t="str">
+        <v/>
+      </c>
+      <c r="K10" t="str">
+        <v/>
+      </c>
+      <c r="L10">
+        <v>2</v>
+      </c>
+      <c r="M10" t="str">
+        <v/>
+      </c>
+      <c r="N10" t="str">
+        <v/>
+      </c>
+      <c r="O10" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="str">
+        <v>2026-07-01</v>
+      </c>
+      <c r="B11" t="str">
+        <v>ONB-5048</v>
+      </c>
+      <c r="C11" t="str">
+        <v>IPH-128GB-BLA</v>
+      </c>
+      <c r="D11" t="str">
+        <v>350100000388031</v>
+      </c>
+      <c r="E11" t="str">
+        <v>NORTHSIDE STOCK</v>
+      </c>
+      <c r="F11">
+        <v>232.81</v>
+      </c>
+      <c r="G11">
+        <v>298.59</v>
+      </c>
+      <c r="H11">
+        <v>65.77999999999997</v>
+      </c>
+      <c r="I11" t="str">
+        <v/>
+      </c>
+      <c r="J11" t="str">
+        <v/>
+      </c>
+      <c r="K11" t="str">
+        <v/>
+      </c>
+      <c r="L11">
+        <v>6.3</v>
+      </c>
+      <c r="M11" t="str">
+        <v/>
+      </c>
+      <c r="N11" t="str">
+        <v/>
+      </c>
+      <c r="O11" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="str">
+        <v>2026-07-06</v>
+      </c>
+      <c r="B12" t="str">
+        <v>ONB-5053</v>
+      </c>
+      <c r="C12" t="str">
+        <v>SAM-128GB-STA</v>
+      </c>
+      <c r="D12" t="str">
+        <v>350100000419707</v>
+      </c>
+      <c r="E12" t="str">
+        <v>MOBILE WHOLESALE LTD</v>
+      </c>
+      <c r="F12">
+        <v>243.53</v>
+      </c>
+      <c r="G12">
+        <v>336.62</v>
+      </c>
+      <c r="H12">
+        <v>93.09</v>
+      </c>
+      <c r="I12" t="str">
+        <v/>
+      </c>
+      <c r="J12" t="str">
+        <v/>
+      </c>
+      <c r="K12" t="str">
+        <v/>
+      </c>
+      <c r="L12">
+        <v>8</v>
+      </c>
+      <c r="M12" t="str">
+        <v/>
+      </c>
+      <c r="N12" t="str">
+        <v/>
+      </c>
+      <c r="O12" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="str">
+        <v>2026-07-11</v>
+      </c>
+      <c r="B13" t="str">
+        <v>ONB-5058</v>
+      </c>
+      <c r="C13" t="str">
+        <v>IPH-128GB-WHI</v>
+      </c>
+      <c r="D13" t="str">
+        <v>350100000459302</v>
+      </c>
+      <c r="E13" t="str">
+        <v>PHONEBOX DIRECT</v>
+      </c>
+      <c r="F13">
+        <v>336.42</v>
+      </c>
+      <c r="G13">
+        <v>468.11</v>
+      </c>
+      <c r="H13">
+        <v>131.69</v>
+      </c>
+      <c r="I13" t="str">
+        <v/>
+      </c>
+      <c r="J13" t="str">
+        <v/>
+      </c>
+      <c r="K13" t="str">
+        <v/>
+      </c>
+      <c r="L13">
+        <v>8</v>
+      </c>
+      <c r="M13" t="str">
+        <v/>
+      </c>
+      <c r="N13" t="str">
+        <v/>
+      </c>
+      <c r="O13" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="str">
+        <v>2026-07-16</v>
+      </c>
+      <c r="B14" t="str">
+        <v>ONB-5063</v>
+      </c>
+      <c r="C14" t="str">
+        <v>GOO-128GB-BLU</v>
+      </c>
+      <c r="D14" t="str">
+        <v>350100000498897</v>
+      </c>
+      <c r="E14" t="str">
+        <v>CELLHUB TRADING</v>
+      </c>
+      <c r="F14">
+        <v>287.02</v>
+      </c>
+      <c r="G14">
+        <v>379.48</v>
+      </c>
+      <c r="H14">
+        <v>92.46000000000004</v>
+      </c>
+      <c r="I14" t="str">
+        <v/>
+      </c>
+      <c r="J14" t="str">
+        <v/>
+      </c>
+      <c r="K14" t="str">
+        <v/>
+      </c>
+      <c r="L14">
+        <v>8</v>
+      </c>
+      <c r="M14" t="str">
+        <v/>
+      </c>
+      <c r="N14" t="str">
+        <v/>
+      </c>
+      <c r="O14" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="str">
+        <v>2026-07-21</v>
+      </c>
+      <c r="B15" t="str">
+        <v>ONB-5068</v>
+      </c>
+      <c r="C15" t="str">
+        <v>IPH-256GB-MID</v>
+      </c>
+      <c r="D15" t="str">
+        <v>350100000538492</v>
+      </c>
+      <c r="E15" t="str">
+        <v>MOBILE WHOLESALE LTD</v>
+      </c>
+      <c r="F15">
+        <v>482.51</v>
+      </c>
+      <c r="G15">
+        <v>628.06</v>
+      </c>
+      <c r="H15">
+        <v>145.54999999999995</v>
+      </c>
+      <c r="I15" t="str">
+        <v/>
+      </c>
+      <c r="J15" t="str">
+        <v/>
+      </c>
+      <c r="K15" t="str">
+        <v/>
+      </c>
+      <c r="L15">
+        <v>6.3</v>
+      </c>
+      <c r="M15" t="str">
+        <v/>
+      </c>
+      <c r="N15" t="str">
+        <v/>
+      </c>
+      <c r="O15" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="str">
+        <v>2026-07-02</v>
+      </c>
+      <c r="B16" t="str">
+        <v>ONB-5073</v>
+      </c>
+      <c r="C16" t="str">
+        <v>IPH-128GB-MID</v>
+      </c>
+      <c r="D16" t="str">
+        <v>350100000578087</v>
+      </c>
+      <c r="E16" t="str">
+        <v>NORTHSIDE STOCK</v>
+      </c>
+      <c r="F16">
+        <v>222.91</v>
+      </c>
+      <c r="G16">
+        <v>305.01</v>
+      </c>
+      <c r="H16">
+        <v>82.1</v>
+      </c>
+      <c r="I16" t="str">
+        <v/>
+      </c>
+      <c r="J16" t="str">
+        <v/>
+      </c>
+      <c r="K16" t="str">
+        <v/>
+      </c>
+      <c r="L16">
+        <v>8</v>
+      </c>
+      <c r="M16" t="str">
+        <v/>
+      </c>
+      <c r="N16" t="str">
+        <v/>
+      </c>
+      <c r="O16" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="str">
+        <v>2026-07-07</v>
+      </c>
+      <c r="B17" t="str">
+        <v>ONB-5078</v>
+      </c>
+      <c r="C17" t="str">
+        <v>SAM-256GB-GRE</v>
+      </c>
+      <c r="D17" t="str">
+        <v>350100000617682</v>
+      </c>
+      <c r="E17" t="str">
+        <v>PHONEBOX DIRECT</v>
+      </c>
+      <c r="F17">
+        <v>422.7</v>
+      </c>
+      <c r="G17">
+        <v>601.22</v>
+      </c>
+      <c r="H17">
+        <v>178.52000000000004</v>
+      </c>
+      <c r="I17" t="str">
+        <v/>
+      </c>
+      <c r="J17" t="str">
+        <v/>
+      </c>
+      <c r="K17" t="str">
+        <v/>
+      </c>
+      <c r="L17">
+        <v>2</v>
+      </c>
+      <c r="M17" t="str">
+        <v/>
+      </c>
+      <c r="N17" t="str">
+        <v/>
+      </c>
+      <c r="O17" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="str">
+        <v>2026-07-12</v>
+      </c>
+      <c r="B18" t="str">
+        <v>ONB-5083</v>
+      </c>
+      <c r="C18" t="str">
+        <v>IPH-256GB-PUR</v>
+      </c>
+      <c r="D18" t="str">
+        <v>350100000657277</v>
+      </c>
+      <c r="E18" t="str">
+        <v>MOBILE WHOLESALE LTD</v>
+      </c>
+      <c r="F18">
+        <v>511.35</v>
+      </c>
+      <c r="G18">
+        <v>700.16</v>
+      </c>
+      <c r="H18">
+        <v>188.80999999999995</v>
+      </c>
+      <c r="I18" t="str">
+        <v/>
+      </c>
+      <c r="J18" t="str">
+        <v/>
+      </c>
+      <c r="K18" t="str">
+        <v/>
+      </c>
+      <c r="L18">
+        <v>2</v>
+      </c>
+      <c r="M18" t="str">
+        <v/>
+      </c>
+      <c r="N18" t="str">
+        <v/>
+      </c>
+      <c r="O18" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="str">
+        <v>2026-07-17</v>
+      </c>
+      <c r="B19" t="str">
+        <v>ONB-5088</v>
+      </c>
+      <c r="C19" t="str">
+        <v>IPH-64GB-STA</v>
+      </c>
+      <c r="D19" t="str">
+        <v>350100000696872</v>
+      </c>
+      <c r="E19" t="str">
+        <v>NORTHSIDE STOCK</v>
+      </c>
+      <c r="F19">
+        <v>186.57</v>
+      </c>
+      <c r="G19">
+        <v>264.87</v>
+      </c>
+      <c r="H19">
+        <v>78.30000000000001</v>
+      </c>
+      <c r="I19" t="str">
+        <v/>
+      </c>
+      <c r="J19" t="str">
+        <v/>
+      </c>
+      <c r="K19" t="str">
+        <v/>
+      </c>
+      <c r="L19">
+        <v>8</v>
+      </c>
+      <c r="M19" t="str">
+        <v/>
+      </c>
+      <c r="N19" t="str">
+        <v/>
+      </c>
+      <c r="O19" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="str">
+        <v>2026-07-22</v>
+      </c>
+      <c r="B20" t="str">
+        <v>ONB-5093</v>
+      </c>
+      <c r="C20" t="str">
+        <v>SAM-128GB-MID</v>
+      </c>
+      <c r="D20" t="str">
+        <v>350100007863567</v>
+      </c>
+      <c r="E20" t="str">
+        <v>NORTHSIDE STOCK</v>
+      </c>
+      <c r="F20">
+        <v>242</v>
+      </c>
+      <c r="G20">
+        <v>353.11</v>
+      </c>
+      <c r="H20">
+        <v>111.11000000000001</v>
+      </c>
+      <c r="I20" t="str">
+        <v/>
+      </c>
+      <c r="J20" t="str">
+        <v/>
+      </c>
+      <c r="K20" t="str">
+        <v/>
+      </c>
+      <c r="L20">
+        <v>8</v>
+      </c>
+      <c r="M20" t="str">
+        <v/>
+      </c>
+      <c r="N20" t="str">
+        <v/>
+      </c>
+      <c r="O20" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="str">
+        <v>2026-07-03</v>
+      </c>
+      <c r="B21" t="str">
+        <v>ONB-5098</v>
+      </c>
+      <c r="C21" t="str">
+        <v>IPH-128GB-BLA</v>
+      </c>
+      <c r="D21" t="str">
+        <v>350100007903162</v>
+      </c>
+      <c r="E21" t="str">
+        <v>CELLHUB TRADING</v>
+      </c>
+      <c r="F21">
+        <v>327.58</v>
+      </c>
+      <c r="G21">
+        <v>485.49</v>
+      </c>
+      <c r="H21">
+        <v>157.91000000000003</v>
+      </c>
+      <c r="I21" t="str">
+        <v/>
+      </c>
+      <c r="J21" t="str">
+        <v/>
+      </c>
+      <c r="K21" t="str">
+        <v/>
+      </c>
+      <c r="L21">
+        <v>8</v>
+      </c>
+      <c r="M21" t="str">
+        <v/>
+      </c>
+      <c r="N21" t="str">
+        <v/>
+      </c>
+      <c r="O21" t="str">
+        <v/>
+      </c>
+    </row>
+  </sheetData>
+  <ignoredErrors>
+    <ignoredError numberStoredAsText="1" sqref="A1:O21"/>
+  </ignoredErrors>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:S21"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="str">
+        <v>Date</v>
+      </c>
+      <c r="B1" t="str">
+        <v>Order Number</v>
+      </c>
+      <c r="C1" t="str">
+        <v>SKU</v>
+      </c>
+      <c r="D1" t="str">
+        <v>IMEI</v>
+      </c>
+      <c r="E1" t="str">
+        <v>Supplier</v>
+      </c>
+      <c r="F1" t="str">
+        <v>Quantity</v>
+      </c>
+      <c r="G1" t="str">
+        <v>BP</v>
+      </c>
+      <c r="H1" t="str">
+        <v>SP</v>
+      </c>
+      <c r="I1" t="str">
+        <v>SP-BP</v>
+      </c>
+      <c r="J1" t="str">
+        <v>Marginal Tax</v>
+      </c>
+      <c r="K1" t="str">
+        <v>Commission</v>
+      </c>
+      <c r="L1" t="str">
+        <v>Commission VAT</v>
+      </c>
+      <c r="M1" t="str">
+        <v>Postage</v>
+      </c>
+      <c r="N1" t="str">
+        <v>P. VAT</v>
+      </c>
+      <c r="O1" t="str">
+        <v>Acc</v>
+      </c>
+      <c r="P1" t="str">
+        <v>Total VAT</v>
+      </c>
+      <c r="Q1" t="str">
+        <v>GP</v>
+      </c>
+      <c r="R1" t="str">
+        <v>GP %</v>
+      </c>
+      <c r="S1" t="str">
+        <v>Total VAT NTP</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="str">
+        <v>2026-07-05</v>
+      </c>
+      <c r="B2" t="str">
+        <v>TEM-5004</v>
+      </c>
+      <c r="C2" t="str">
+        <v>IPH-256GB-PUR</v>
+      </c>
+      <c r="D2" t="str">
+        <v>350100000031676</v>
+      </c>
+      <c r="E2" t="str">
+        <v>NORTHSIDE STOCK</v>
+      </c>
+      <c r="F2">
+        <v>1</v>
+      </c>
+      <c r="G2">
+        <v>459.49</v>
+      </c>
+      <c r="H2">
+        <v>653.1</v>
+      </c>
+      <c r="I2">
+        <v>193.61</v>
+      </c>
+      <c r="J2" t="str">
+        <v/>
+      </c>
+      <c r="K2">
+        <v>53.55</v>
+      </c>
+      <c r="L2">
+        <v>10.71</v>
+      </c>
+      <c r="M2">
+        <v>2</v>
+      </c>
+      <c r="N2" t="str">
+        <v/>
+      </c>
+      <c r="O2" t="str">
+        <v/>
+      </c>
+      <c r="P2" t="str">
+        <v/>
+      </c>
+      <c r="Q2" t="str">
+        <v/>
+      </c>
+      <c r="R2" t="str">
+        <v/>
+      </c>
+      <c r="S2" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="str">
+        <v>2026-07-10</v>
+      </c>
+      <c r="B3" t="str">
+        <v>TEM-5009</v>
+      </c>
+      <c r="C3" t="str">
+        <v>IPH-128GB-WHI</v>
+      </c>
+      <c r="D3" t="str">
+        <v>350100000071271</v>
       </c>
       <c r="E3" t="str">
         <v>CELLHUB TRADING</v>
       </c>
       <c r="F3">
-        <v>260.29</v>
+        <v>1</v>
       </c>
       <c r="G3">
-        <v>329.11</v>
+        <v>229.85</v>
       </c>
       <c r="H3">
-        <v>68.82</v>
-      </c>
-      <c r="I3" t="str">
-        <v/>
+        <v>322.37</v>
+      </c>
+      <c r="I3">
+        <v>92.52000000000001</v>
       </c>
       <c r="J3" t="str">
         <v/>
       </c>
-      <c r="K3" t="str">
-        <v/>
+      <c r="K3">
+        <v>26.43</v>
       </c>
       <c r="L3">
-        <v>6.3</v>
-      </c>
-      <c r="M3" t="str">
-        <v/>
+        <v>5.29</v>
+      </c>
+      <c r="M3">
+        <v>8</v>
       </c>
       <c r="N3" t="str">
         <v/>
       </c>
       <c r="O3" t="str">
+        <v/>
+      </c>
+      <c r="P3" t="str">
+        <v/>
+      </c>
+      <c r="Q3" t="str">
+        <v/>
+      </c>
+      <c r="R3" t="str">
+        <v/>
+      </c>
+      <c r="S3" t="str">
         <v/>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>2026-07-12</v>
+        <v>2026-07-15</v>
       </c>
       <c r="B4" t="str">
-        <v>ONB-5011</v>
+        <v>TEM-5014</v>
       </c>
       <c r="C4" t="str">
-        <v>IPH-256GB-BLA</v>
+        <v>SAM-256GB-WHI</v>
       </c>
       <c r="D4" t="str">
-        <v>350100000087109</v>
+        <v>350100000110866</v>
       </c>
       <c r="E4" t="str">
-        <v>MOBILE WHOLESALE LTD</v>
+        <v>PHONEBOX DIRECT</v>
       </c>
       <c r="F4">
-        <v>514.23</v>
+        <v>1</v>
       </c>
       <c r="G4">
-        <v>660.92</v>
+        <v>450.57</v>
       </c>
       <c r="H4">
-        <v>146.68999999999994</v>
-      </c>
-      <c r="I4" t="str">
-        <v/>
+        <v>603.85</v>
+      </c>
+      <c r="I4">
+        <v>153.28000000000003</v>
       </c>
       <c r="J4" t="str">
         <v/>
       </c>
-      <c r="K4" t="str">
-        <v/>
+      <c r="K4">
+        <v>27.78</v>
       </c>
       <c r="L4">
-        <v>8</v>
-      </c>
-      <c r="M4" t="str">
-        <v/>
+        <v>5.56</v>
+      </c>
+      <c r="M4">
+        <v>2</v>
       </c>
       <c r="N4" t="str">
         <v/>
       </c>
       <c r="O4" t="str">
+        <v/>
+      </c>
+      <c r="P4" t="str">
+        <v/>
+      </c>
+      <c r="Q4" t="str">
+        <v/>
+      </c>
+      <c r="R4" t="str">
+        <v/>
+      </c>
+      <c r="S4" t="str">
         <v/>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>2026-07-16</v>
+        <v>2026-07-20</v>
       </c>
       <c r="B5" t="str">
-        <v>ONB-5015</v>
+        <v>TEM-5019</v>
       </c>
       <c r="C5" t="str">
-        <v>GOO-128GB-BLA</v>
+        <v>IPH-256GB-GRA</v>
       </c>
       <c r="D5" t="str">
-        <v>350100000118785</v>
+        <v>350100000150461</v>
       </c>
       <c r="E5" t="str">
-        <v>PHONEBOX DIRECT</v>
+        <v>CELLHUB TRADING</v>
       </c>
       <c r="F5">
-        <v>280.37</v>
+        <v>1</v>
       </c>
       <c r="G5">
-        <v>418.03</v>
+        <v>529.23</v>
       </c>
       <c r="H5">
-        <v>137.65999999999997</v>
-      </c>
-      <c r="I5" t="str">
-        <v/>
+        <v>740.45</v>
+      </c>
+      <c r="I5">
+        <v>211.22000000000003</v>
       </c>
       <c r="J5" t="str">
         <v/>
       </c>
-      <c r="K5" t="str">
-        <v/>
+      <c r="K5">
+        <v>34.06</v>
       </c>
       <c r="L5">
+        <v>6.81</v>
+      </c>
+      <c r="M5">
         <v>8</v>
       </c>
-      <c r="M5" t="str">
-        <v/>
-      </c>
       <c r="N5" t="str">
         <v/>
       </c>
       <c r="O5" t="str">
+        <v/>
+      </c>
+      <c r="P5" t="str">
+        <v/>
+      </c>
+      <c r="Q5" t="str">
+        <v/>
+      </c>
+      <c r="R5" t="str">
+        <v/>
+      </c>
+      <c r="S5" t="str">
         <v/>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>2026-07-20</v>
+        <v>2026-07-01</v>
       </c>
       <c r="B6" t="str">
-        <v>ONB-5019</v>
+        <v>TEM-5024</v>
       </c>
       <c r="C6" t="str">
-        <v>IPH-256GB-GRA</v>
+        <v>IPH-128GB-STA</v>
       </c>
       <c r="D6" t="str">
-        <v>350100000150461</v>
+        <v>350100000197975</v>
       </c>
       <c r="E6" t="str">
-        <v>CELLHUB TRADING</v>
+        <v>PHONEBOX DIRECT</v>
       </c>
       <c r="F6">
-        <v>529.23</v>
+        <v>1</v>
       </c>
       <c r="G6">
-        <v>685.84</v>
+        <v>233.36</v>
       </c>
       <c r="H6">
-        <v>156.61</v>
-      </c>
-      <c r="I6" t="str">
-        <v/>
+        <v>306.12</v>
+      </c>
+      <c r="I6">
+        <v>72.75999999999999</v>
       </c>
       <c r="J6" t="str">
         <v/>
       </c>
-      <c r="K6" t="str">
-        <v/>
+      <c r="K6">
+        <v>21.43</v>
       </c>
       <c r="L6">
-        <v>6.3</v>
-      </c>
-      <c r="M6" t="str">
-        <v/>
+        <v>4.29</v>
+      </c>
+      <c r="M6">
+        <v>8</v>
       </c>
       <c r="N6" t="str">
         <v/>
       </c>
       <c r="O6" t="str">
+        <v/>
+      </c>
+      <c r="P6" t="str">
+        <v/>
+      </c>
+      <c r="Q6" t="str">
+        <v/>
+      </c>
+      <c r="R6" t="str">
+        <v/>
+      </c>
+      <c r="S6" t="str">
         <v/>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>2026-07-24</v>
+        <v>2026-07-06</v>
       </c>
       <c r="B7" t="str">
-        <v>ONB-5023</v>
+        <v>TEM-5029</v>
       </c>
       <c r="C7" t="str">
-        <v>GOO-128GB-BLA</v>
+        <v>SAM-128GB-WHI</v>
       </c>
       <c r="D7" t="str">
-        <v>350100000182137</v>
+        <v>350100000229651</v>
       </c>
       <c r="E7" t="str">
-        <v>CELLHUB TRADING</v>
+        <v>NORTHSIDE STOCK</v>
       </c>
       <c r="F7">
-        <v>276.86</v>
+        <v>1</v>
       </c>
       <c r="G7">
-        <v>386.46</v>
+        <v>253.86</v>
       </c>
       <c r="H7">
-        <v>109.59999999999997</v>
-      </c>
-      <c r="I7" t="str">
-        <v/>
+        <v>371.8</v>
+      </c>
+      <c r="I7">
+        <v>117.94</v>
       </c>
       <c r="J7" t="str">
         <v/>
       </c>
-      <c r="K7" t="str">
-        <v/>
+      <c r="K7">
+        <v>17.1</v>
       </c>
       <c r="L7">
-        <v>6.3</v>
-      </c>
-      <c r="M7" t="str">
-        <v/>
+        <v>3.42</v>
+      </c>
+      <c r="M7">
+        <v>8</v>
       </c>
       <c r="N7" t="str">
         <v/>
       </c>
       <c r="O7" t="str">
+        <v/>
+      </c>
+      <c r="P7" t="str">
+        <v/>
+      </c>
+      <c r="Q7" t="str">
+        <v/>
+      </c>
+      <c r="R7" t="str">
+        <v/>
+      </c>
+      <c r="S7" t="str">
         <v/>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>2026-07-04</v>
+        <v>2026-07-11</v>
       </c>
       <c r="B8" t="str">
-        <v>ONB-5027</v>
+        <v>TEM-5034</v>
       </c>
       <c r="C8" t="str">
-        <v>IPH-256GB-MID</v>
+        <v>IPH-128GB-GRE</v>
       </c>
       <c r="D8" t="str">
-        <v>350100000213813</v>
+        <v>350100000269246</v>
       </c>
       <c r="E8" t="str">
-        <v>PHONEBOX DIRECT</v>
+        <v>CELLHUB TRADING</v>
       </c>
       <c r="F8">
-        <v>499.91</v>
+        <v>1</v>
       </c>
       <c r="G8">
-        <v>712.92</v>
+        <v>305.4</v>
       </c>
       <c r="H8">
-        <v>213.00999999999993</v>
-      </c>
-      <c r="I8" t="str">
-        <v/>
+        <v>390.8</v>
+      </c>
+      <c r="I8">
+        <v>85.40000000000003</v>
       </c>
       <c r="J8" t="str">
         <v/>
       </c>
-      <c r="K8" t="str">
-        <v/>
+      <c r="K8">
+        <v>21.49</v>
       </c>
       <c r="L8">
+        <v>4.3</v>
+      </c>
+      <c r="M8">
         <v>8</v>
       </c>
-      <c r="M8" t="str">
-        <v/>
-      </c>
       <c r="N8" t="str">
         <v/>
       </c>
       <c r="O8" t="str">
+        <v/>
+      </c>
+      <c r="P8" t="str">
+        <v/>
+      </c>
+      <c r="Q8" t="str">
+        <v/>
+      </c>
+      <c r="R8" t="str">
+        <v/>
+      </c>
+      <c r="S8" t="str">
         <v/>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>2026-07-08</v>
+        <v>2026-07-16</v>
       </c>
       <c r="B9" t="str">
-        <v>ONB-5031</v>
+        <v>TEM-5039</v>
       </c>
       <c r="C9" t="str">
-        <v>GOO-128GB-GRE</v>
+        <v>GOO-128GB-GRA</v>
       </c>
       <c r="D9" t="str">
-        <v>350100000245489</v>
+        <v>350100000308841</v>
       </c>
       <c r="E9" t="str">
         <v>MOBILE WHOLESALE LTD</v>
       </c>
       <c r="F9">
-        <v>290.37</v>
+        <v>1</v>
       </c>
       <c r="G9">
-        <v>388.18</v>
+        <v>268.59</v>
       </c>
       <c r="H9">
-        <v>97.81</v>
-      </c>
-      <c r="I9" t="str">
-        <v/>
+        <v>354.91</v>
+      </c>
+      <c r="I9">
+        <v>86.32000000000005</v>
       </c>
       <c r="J9" t="str">
         <v/>
       </c>
-      <c r="K9" t="str">
-        <v/>
+      <c r="K9">
+        <v>16.33</v>
       </c>
       <c r="L9">
+        <v>3.27</v>
+      </c>
+      <c r="M9">
         <v>8</v>
       </c>
-      <c r="M9" t="str">
-        <v/>
-      </c>
       <c r="N9" t="str">
         <v/>
       </c>
       <c r="O9" t="str">
+        <v/>
+      </c>
+      <c r="P9" t="str">
+        <v/>
+      </c>
+      <c r="Q9" t="str">
+        <v/>
+      </c>
+      <c r="R9" t="str">
+        <v/>
+      </c>
+      <c r="S9" t="str">
         <v/>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>2026-07-12</v>
+        <v>2026-07-21</v>
       </c>
       <c r="B10" t="str">
-        <v>ONB-5035</v>
+        <v>TEM-5044</v>
       </c>
       <c r="C10" t="str">
-        <v>IPH-256GB-GRE</v>
+        <v>IPH-256GB-MID</v>
       </c>
       <c r="D10" t="str">
-        <v>350100000277165</v>
+        <v>350100000348436</v>
       </c>
       <c r="E10" t="str">
-        <v>CELLHUB TRADING</v>
+        <v>MOBILE WHOLESALE LTD</v>
       </c>
       <c r="F10">
-        <v>495.98</v>
+        <v>1</v>
       </c>
       <c r="G10">
-        <v>706.88</v>
+        <v>484.06</v>
       </c>
       <c r="H10">
-        <v>210.89999999999998</v>
-      </c>
-      <c r="I10" t="str">
-        <v/>
+        <v>721.16</v>
+      </c>
+      <c r="I10">
+        <v>237.09999999999997</v>
       </c>
       <c r="J10" t="str">
         <v/>
       </c>
-      <c r="K10" t="str">
-        <v/>
+      <c r="K10">
+        <v>59.14</v>
       </c>
       <c r="L10">
-        <v>8</v>
-      </c>
-      <c r="M10" t="str">
-        <v/>
+        <v>11.83</v>
+      </c>
+      <c r="M10">
+        <v>2</v>
       </c>
       <c r="N10" t="str">
         <v/>
       </c>
       <c r="O10" t="str">
+        <v/>
+      </c>
+      <c r="P10" t="str">
+        <v/>
+      </c>
+      <c r="Q10" t="str">
+        <v/>
+      </c>
+      <c r="R10" t="str">
+        <v/>
+      </c>
+      <c r="S10" t="str">
         <v/>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>2026-07-16</v>
+        <v>2026-07-02</v>
       </c>
       <c r="B11" t="str">
-        <v>ONB-5039</v>
+        <v>TEM-5049</v>
       </c>
       <c r="C11" t="str">
-        <v>GOO-128GB-GRA</v>
+        <v>IPH-128GB-BLA</v>
       </c>
       <c r="D11" t="str">
-        <v>350100000308841</v>
+        <v>350100000388031</v>
       </c>
       <c r="E11" t="str">
-        <v>MOBILE WHOLESALE LTD</v>
+        <v>NORTHSIDE STOCK</v>
       </c>
       <c r="F11">
-        <v>268.59</v>
+        <v>1</v>
       </c>
       <c r="G11">
-        <v>369.04</v>
+        <v>232.81</v>
       </c>
       <c r="H11">
-        <v>100.45000000000005</v>
-      </c>
-      <c r="I11" t="str">
-        <v/>
+        <v>319.12</v>
+      </c>
+      <c r="I11">
+        <v>86.31</v>
       </c>
       <c r="J11" t="str">
         <v/>
       </c>
-      <c r="K11" t="str">
-        <v/>
+      <c r="K11">
+        <v>26.17</v>
       </c>
       <c r="L11">
-        <v>2</v>
-      </c>
-      <c r="M11" t="str">
-        <v/>
+        <v>5.23</v>
+      </c>
+      <c r="M11">
+        <v>8</v>
       </c>
       <c r="N11" t="str">
         <v/>
       </c>
       <c r="O11" t="str">
+        <v/>
+      </c>
+      <c r="P11" t="str">
+        <v/>
+      </c>
+      <c r="Q11" t="str">
+        <v/>
+      </c>
+      <c r="R11" t="str">
+        <v/>
+      </c>
+      <c r="S11" t="str">
         <v/>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>2026-07-20</v>
+        <v>2026-07-07</v>
       </c>
       <c r="B12" t="str">
-        <v>ONB-5043</v>
+        <v>TEM-5054</v>
       </c>
       <c r="C12" t="str">
-        <v>IPH-256GB-STA</v>
+        <v>SAM-256GB-GRA</v>
       </c>
       <c r="D12" t="str">
-        <v>350100000340517</v>
+        <v>350100000427626</v>
       </c>
       <c r="E12" t="str">
         <v>NORTHSIDE STOCK</v>
       </c>
       <c r="F12">
-        <v>500.85</v>
+        <v>1</v>
       </c>
       <c r="G12">
-        <v>661.97</v>
+        <v>405.86</v>
       </c>
       <c r="H12">
-        <v>161.12</v>
-      </c>
-      <c r="I12" t="str">
-        <v/>
+        <v>574.95</v>
+      </c>
+      <c r="I12">
+        <v>169.09000000000003</v>
       </c>
       <c r="J12" t="str">
         <v/>
       </c>
-      <c r="K12" t="str">
-        <v/>
+      <c r="K12">
+        <v>31.62</v>
       </c>
       <c r="L12">
+        <v>6.32</v>
+      </c>
+      <c r="M12">
         <v>8</v>
       </c>
-      <c r="M12" t="str">
-        <v/>
-      </c>
       <c r="N12" t="str">
         <v/>
       </c>
       <c r="O12" t="str">
+        <v/>
+      </c>
+      <c r="P12" t="str">
+        <v/>
+      </c>
+      <c r="Q12" t="str">
+        <v/>
+      </c>
+      <c r="R12" t="str">
+        <v/>
+      </c>
+      <c r="S12" t="str">
         <v/>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>2026-07-24</v>
+        <v>2026-07-12</v>
       </c>
       <c r="B13" t="str">
-        <v>ONB-5047</v>
+        <v>TEM-5059</v>
       </c>
       <c r="C13" t="str">
-        <v>GOO-128GB-GRA</v>
+        <v>IPH-256GB-BLA</v>
       </c>
       <c r="D13" t="str">
-        <v>350100000372193</v>
+        <v>350100000467221</v>
       </c>
       <c r="E13" t="str">
-        <v>CELLHUB TRADING</v>
+        <v>PHONEBOX DIRECT</v>
       </c>
       <c r="F13">
-        <v>256.93</v>
+        <v>1</v>
       </c>
       <c r="G13">
-        <v>380.8</v>
+        <v>507.95</v>
       </c>
       <c r="H13">
-        <v>123.87</v>
-      </c>
-      <c r="I13" t="str">
-        <v/>
+        <v>670.51</v>
+      </c>
+      <c r="I13">
+        <v>162.56</v>
       </c>
       <c r="J13" t="str">
         <v/>
       </c>
-      <c r="K13" t="str">
-        <v/>
+      <c r="K13">
+        <v>36.88</v>
       </c>
       <c r="L13">
-        <v>2</v>
-      </c>
-      <c r="M13" t="str">
-        <v/>
+        <v>7.38</v>
+      </c>
+      <c r="M13">
+        <v>8</v>
       </c>
       <c r="N13" t="str">
         <v/>
       </c>
       <c r="O13" t="str">
+        <v/>
+      </c>
+      <c r="P13" t="str">
+        <v/>
+      </c>
+      <c r="Q13" t="str">
+        <v/>
+      </c>
+      <c r="R13" t="str">
+        <v/>
+      </c>
+      <c r="S13" t="str">
         <v/>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>2026-07-04</v>
+        <v>2026-07-17</v>
       </c>
       <c r="B14" t="str">
-        <v>ONB-5051</v>
+        <v>TEM-5064</v>
       </c>
       <c r="C14" t="str">
-        <v>IPH-256GB-GRE</v>
+        <v>IPH-64GB-GRE</v>
       </c>
       <c r="D14" t="str">
-        <v>350100000403869</v>
+        <v>350100000506816</v>
       </c>
       <c r="E14" t="str">
-        <v>PHONEBOX DIRECT</v>
+        <v>MOBILE WHOLESALE LTD</v>
       </c>
       <c r="F14">
-        <v>533.2</v>
+        <v>1</v>
       </c>
       <c r="G14">
-        <v>683.86</v>
+        <v>197.28</v>
       </c>
       <c r="H14">
-        <v>150.65999999999997</v>
-      </c>
-      <c r="I14" t="str">
-        <v/>
+        <v>253.57</v>
+      </c>
+      <c r="I14">
+        <v>56.28999999999999</v>
       </c>
       <c r="J14" t="str">
         <v/>
       </c>
-      <c r="K14" t="str">
-        <v/>
+      <c r="K14">
+        <v>17.75</v>
       </c>
       <c r="L14">
-        <v>6.3</v>
-      </c>
-      <c r="M14" t="str">
-        <v/>
+        <v>3.55</v>
+      </c>
+      <c r="M14">
+        <v>8</v>
       </c>
       <c r="N14" t="str">
         <v/>
       </c>
       <c r="O14" t="str">
+        <v/>
+      </c>
+      <c r="P14" t="str">
+        <v/>
+      </c>
+      <c r="Q14" t="str">
+        <v/>
+      </c>
+      <c r="R14" t="str">
+        <v/>
+      </c>
+      <c r="S14" t="str">
         <v/>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>2026-07-08</v>
+        <v>2026-07-22</v>
       </c>
       <c r="B15" t="str">
-        <v>ONB-5055</v>
+        <v>TEM-5069</v>
       </c>
       <c r="C15" t="str">
-        <v>GOO-128GB-MID</v>
+        <v>SAM-128GB-BLU</v>
       </c>
       <c r="D15" t="str">
-        <v>350100000435545</v>
+        <v>350100000546411</v>
       </c>
       <c r="E15" t="str">
         <v>MOBILE WHOLESALE LTD</v>
       </c>
       <c r="F15">
-        <v>267</v>
+        <v>1</v>
       </c>
       <c r="G15">
-        <v>358.72</v>
+        <v>263.11</v>
       </c>
       <c r="H15">
-        <v>91.72000000000003</v>
-      </c>
-      <c r="I15" t="str">
-        <v/>
+        <v>334.65</v>
+      </c>
+      <c r="I15">
+        <v>71.53999999999996</v>
       </c>
       <c r="J15" t="str">
         <v/>
       </c>
-      <c r="K15" t="str">
-        <v/>
+      <c r="K15">
+        <v>18.41</v>
       </c>
       <c r="L15">
-        <v>8</v>
-      </c>
-      <c r="M15" t="str">
-        <v/>
+        <v>3.68</v>
+      </c>
+      <c r="M15">
+        <v>2</v>
       </c>
       <c r="N15" t="str">
         <v/>
       </c>
       <c r="O15" t="str">
+        <v/>
+      </c>
+      <c r="P15" t="str">
+        <v/>
+      </c>
+      <c r="Q15" t="str">
+        <v/>
+      </c>
+      <c r="R15" t="str">
+        <v/>
+      </c>
+      <c r="S15" t="str">
         <v/>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>2026-07-12</v>
+        <v>2026-07-03</v>
       </c>
       <c r="B16" t="str">
-        <v>ONB-5059</v>
+        <v>TEM-5074</v>
       </c>
       <c r="C16" t="str">
-        <v>IPH-256GB-BLA</v>
+        <v>IPH-128GB-PUR</v>
       </c>
       <c r="D16" t="str">
-        <v>350100000467221</v>
+        <v>350100000586006</v>
       </c>
       <c r="E16" t="str">
-        <v>PHONEBOX DIRECT</v>
+        <v>NORTHSIDE STOCK</v>
       </c>
       <c r="F16">
-        <v>507.95</v>
+        <v>1</v>
       </c>
       <c r="G16">
-        <v>658.85</v>
+        <v>334.66</v>
       </c>
       <c r="H16">
-        <v>150.90000000000003</v>
-      </c>
-      <c r="I16" t="str">
-        <v/>
+        <v>466.67</v>
+      </c>
+      <c r="I16">
+        <v>132.01</v>
       </c>
       <c r="J16" t="str">
         <v/>
       </c>
-      <c r="K16" t="str">
-        <v/>
+      <c r="K16">
+        <v>38.27</v>
       </c>
       <c r="L16">
+        <v>7.65</v>
+      </c>
+      <c r="M16">
         <v>8</v>
       </c>
-      <c r="M16" t="str">
-        <v/>
-      </c>
       <c r="N16" t="str">
         <v/>
       </c>
       <c r="O16" t="str">
+        <v/>
+      </c>
+      <c r="P16" t="str">
+        <v/>
+      </c>
+      <c r="Q16" t="str">
+        <v/>
+      </c>
+      <c r="R16" t="str">
+        <v/>
+      </c>
+      <c r="S16" t="str">
         <v/>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v>2026-07-16</v>
+        <v>2026-07-08</v>
       </c>
       <c r="B17" t="str">
-        <v>ONB-5063</v>
+        <v>TEM-5079</v>
       </c>
       <c r="C17" t="str">
-        <v>GOO-128GB-BLU</v>
+        <v>GOO-128GB-WHI</v>
       </c>
       <c r="D17" t="str">
-        <v>350100000498897</v>
+        <v>350100000625601</v>
       </c>
       <c r="E17" t="str">
-        <v>CELLHUB TRADING</v>
+        <v>MOBILE WHOLESALE LTD</v>
       </c>
       <c r="F17">
-        <v>287.02</v>
+        <v>1</v>
       </c>
       <c r="G17">
-        <v>373.16</v>
+        <v>262.14</v>
       </c>
       <c r="H17">
-        <v>86.14000000000004</v>
-      </c>
-      <c r="I17" t="str">
-        <v/>
+        <v>338.57</v>
+      </c>
+      <c r="I17">
+        <v>76.43</v>
       </c>
       <c r="J17" t="str">
         <v/>
       </c>
-      <c r="K17" t="str">
-        <v/>
+      <c r="K17">
+        <v>23.7</v>
       </c>
       <c r="L17">
-        <v>8</v>
-      </c>
-      <c r="M17" t="str">
-        <v/>
+        <v>4.74</v>
+      </c>
+      <c r="M17">
+        <v>6.3</v>
       </c>
       <c r="N17" t="str">
         <v/>
       </c>
       <c r="O17" t="str">
+        <v/>
+      </c>
+      <c r="P17" t="str">
+        <v/>
+      </c>
+      <c r="Q17" t="str">
+        <v/>
+      </c>
+      <c r="R17" t="str">
+        <v/>
+      </c>
+      <c r="S17" t="str">
         <v/>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v>2026-07-20</v>
+        <v>2026-07-13</v>
       </c>
       <c r="B18" t="str">
-        <v>ONB-5067</v>
+        <v>TEM-5084</v>
       </c>
       <c r="C18" t="str">
-        <v>IPH-256GB-GRA</v>
+        <v>SAM-128GB-GRA</v>
       </c>
       <c r="D18" t="str">
-        <v>350100000530573</v>
+        <v>350100000673115</v>
       </c>
       <c r="E18" t="str">
-        <v>CELLHUB TRADING</v>
+        <v>NORTHSIDE STOCK</v>
       </c>
       <c r="F18">
-        <v>500.16</v>
+        <v>1</v>
       </c>
       <c r="G18">
-        <v>661.28</v>
+        <v>246.21</v>
       </c>
       <c r="H18">
-        <v>161.11999999999995</v>
-      </c>
-      <c r="I18" t="str">
-        <v/>
+        <v>344.78</v>
+      </c>
+      <c r="I18">
+        <v>98.56999999999996</v>
       </c>
       <c r="J18" t="str">
         <v/>
       </c>
-      <c r="K18" t="str">
-        <v/>
+      <c r="K18">
+        <v>28.27</v>
       </c>
       <c r="L18">
-        <v>8</v>
-      </c>
-      <c r="M18" t="str">
-        <v/>
+        <v>5.65</v>
+      </c>
+      <c r="M18">
+        <v>6.3</v>
       </c>
       <c r="N18" t="str">
         <v/>
       </c>
       <c r="O18" t="str">
+        <v/>
+      </c>
+      <c r="P18" t="str">
+        <v/>
+      </c>
+      <c r="Q18" t="str">
+        <v/>
+      </c>
+      <c r="R18" t="str">
+        <v/>
+      </c>
+      <c r="S18" t="str">
         <v/>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v>2026-07-24</v>
+        <v>2026-07-18</v>
       </c>
       <c r="B19" t="str">
-        <v>ONB-5071</v>
+        <v>TEM-5089</v>
       </c>
       <c r="C19" t="str">
-        <v>GOO-128GB-BLU</v>
+        <v>IPH-128GB-MID</v>
       </c>
       <c r="D19" t="str">
-        <v>350100000562249</v>
+        <v>350100000704791</v>
       </c>
       <c r="E19" t="str">
-        <v>PHONEBOX DIRECT</v>
+        <v>MOBILE WHOLESALE LTD</v>
       </c>
       <c r="F19">
-        <v>264.82</v>
+        <v>1</v>
       </c>
       <c r="G19">
-        <v>348.17</v>
+        <v>227.85</v>
       </c>
       <c r="H19">
-        <v>83.35000000000002</v>
-      </c>
-      <c r="I19" t="str">
-        <v/>
+        <v>304.26</v>
+      </c>
+      <c r="I19">
+        <v>76.41</v>
       </c>
       <c r="J19" t="str">
         <v/>
       </c>
-      <c r="K19" t="str">
-        <v/>
+      <c r="K19">
+        <v>16.73</v>
       </c>
       <c r="L19">
-        <v>2</v>
-      </c>
-      <c r="M19" t="str">
-        <v/>
+        <v>3.35</v>
+      </c>
+      <c r="M19">
+        <v>8</v>
       </c>
       <c r="N19" t="str">
         <v/>
       </c>
       <c r="O19" t="str">
+        <v/>
+      </c>
+      <c r="P19" t="str">
+        <v/>
+      </c>
+      <c r="Q19" t="str">
+        <v/>
+      </c>
+      <c r="R19" t="str">
+        <v/>
+      </c>
+      <c r="S19" t="str">
         <v/>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="str">
-        <v>2026-07-04</v>
+        <v>2026-07-23</v>
       </c>
       <c r="B20" t="str">
-        <v>ONB-5075</v>
+        <v>TEM-5094</v>
       </c>
       <c r="C20" t="str">
-        <v>IPH-256GB-BLA</v>
+        <v>SAM-256GB-PUR</v>
       </c>
       <c r="D20" t="str">
-        <v>350100000593925</v>
+        <v>350100007871486</v>
       </c>
       <c r="E20" t="str">
-        <v>NORTHSIDE STOCK</v>
+        <v>MOBILE WHOLESALE LTD</v>
       </c>
       <c r="F20">
-        <v>501.14</v>
+        <v>1</v>
       </c>
       <c r="G20">
-        <v>742.15</v>
+        <v>417.16</v>
       </c>
       <c r="H20">
-        <v>241.01</v>
-      </c>
-      <c r="I20" t="str">
-        <v/>
+        <v>566.56</v>
+      </c>
+      <c r="I20">
+        <v>149.39999999999992</v>
       </c>
       <c r="J20" t="str">
         <v/>
       </c>
-      <c r="K20" t="str">
-        <v/>
+      <c r="K20">
+        <v>39.66</v>
       </c>
       <c r="L20">
+        <v>7.93</v>
+      </c>
+      <c r="M20">
         <v>6.3</v>
       </c>
-      <c r="M20" t="str">
-        <v/>
-      </c>
       <c r="N20" t="str">
         <v/>
       </c>
       <c r="O20" t="str">
+        <v/>
+      </c>
+      <c r="P20" t="str">
+        <v/>
+      </c>
+      <c r="Q20" t="str">
+        <v/>
+      </c>
+      <c r="R20" t="str">
+        <v/>
+      </c>
+      <c r="S20" t="str">
         <v/>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="str">
-        <v>2026-07-08</v>
+        <v>2026-07-04</v>
       </c>
       <c r="B21" t="str">
-        <v>ONB-5079</v>
+        <v>TEM-5099</v>
       </c>
       <c r="C21" t="str">
-        <v>GOO-128GB-WHI</v>
+        <v>IPH-256GB-BLA</v>
       </c>
       <c r="D21" t="str">
-        <v>350100000625601</v>
+        <v>350100007911081</v>
       </c>
       <c r="E21" t="str">
-        <v>MOBILE WHOLESALE LTD</v>
+        <v>PHONEBOX DIRECT</v>
       </c>
       <c r="F21">
-        <v>262.14</v>
+        <v>1</v>
       </c>
       <c r="G21">
-        <v>340.26</v>
+        <v>517.1</v>
       </c>
       <c r="H21">
-        <v>78.12</v>
-      </c>
-      <c r="I21" t="str">
-        <v/>
+        <v>708.95</v>
+      </c>
+      <c r="I21">
+        <v>191.85000000000002</v>
       </c>
       <c r="J21" t="str">
         <v/>
       </c>
-      <c r="K21" t="str">
-        <v/>
+      <c r="K21">
+        <v>38.99</v>
       </c>
       <c r="L21">
+        <v>7.8</v>
+      </c>
+      <c r="M21">
         <v>2</v>
       </c>
-      <c r="M21" t="str">
-        <v/>
-      </c>
       <c r="N21" t="str">
         <v/>
       </c>
       <c r="O21" t="str">
         <v/>
       </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="str">
-        <v>2026-07-12</v>
-      </c>
-      <c r="B22" t="str">
-        <v>ONB-5083</v>
-      </c>
-      <c r="C22" t="str">
-        <v>IPH-256GB-PUR</v>
-      </c>
-      <c r="D22" t="str">
-        <v>350100000657277</v>
-      </c>
-      <c r="E22" t="str">
-        <v>MOBILE WHOLESALE LTD</v>
-      </c>
-      <c r="F22">
-        <v>511.35</v>
-      </c>
-      <c r="G22">
-        <v>727.31</v>
-      </c>
-      <c r="H22">
-        <v>215.95999999999992</v>
-      </c>
-      <c r="I22" t="str">
-        <v/>
-      </c>
-      <c r="J22" t="str">
-        <v/>
-      </c>
-      <c r="K22" t="str">
-        <v/>
-      </c>
-      <c r="L22">
-        <v>2</v>
-      </c>
-      <c r="M22" t="str">
-        <v/>
-      </c>
-      <c r="N22" t="str">
-        <v/>
-      </c>
-      <c r="O22" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="str">
-        <v>2026-07-16</v>
-      </c>
-      <c r="B23" t="str">
-        <v>ONB-5087</v>
-      </c>
-      <c r="C23" t="str">
-        <v>GOO-128GB-STA</v>
-      </c>
-      <c r="D23" t="str">
-        <v>350100000688953</v>
-      </c>
-      <c r="E23" t="str">
-        <v>PHONEBOX DIRECT</v>
-      </c>
-      <c r="F23">
-        <v>275.49</v>
-      </c>
-      <c r="G23">
-        <v>389.63</v>
-      </c>
-      <c r="H23">
-        <v>114.13999999999999</v>
-      </c>
-      <c r="I23" t="str">
-        <v/>
-      </c>
-      <c r="J23" t="str">
-        <v/>
-      </c>
-      <c r="K23" t="str">
-        <v/>
-      </c>
-      <c r="L23">
-        <v>8</v>
-      </c>
-      <c r="M23" t="str">
-        <v/>
-      </c>
-      <c r="N23" t="str">
-        <v/>
-      </c>
-      <c r="O23" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="str">
-        <v>2026-07-20</v>
-      </c>
-      <c r="B24" t="str">
-        <v>ONB-5091</v>
-      </c>
-      <c r="C24" t="str">
-        <v>IPH-256GB-GRA</v>
-      </c>
-      <c r="D24" t="str">
-        <v>350100007847729</v>
-      </c>
-      <c r="E24" t="str">
-        <v>NORTHSIDE STOCK</v>
-      </c>
-      <c r="F24">
-        <v>530.25</v>
-      </c>
-      <c r="G24">
-        <v>719.58</v>
-      </c>
-      <c r="H24">
-        <v>189.33000000000004</v>
-      </c>
-      <c r="I24" t="str">
-        <v/>
-      </c>
-      <c r="J24" t="str">
-        <v/>
-      </c>
-      <c r="K24" t="str">
-        <v/>
-      </c>
-      <c r="L24">
-        <v>8</v>
-      </c>
-      <c r="M24" t="str">
-        <v/>
-      </c>
-      <c r="N24" t="str">
-        <v/>
-      </c>
-      <c r="O24" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="str">
-        <v>2026-07-24</v>
-      </c>
-      <c r="B25" t="str">
-        <v>ONB-5095</v>
-      </c>
-      <c r="C25" t="str">
-        <v>GOO-128GB-BLU</v>
-      </c>
-      <c r="D25" t="str">
-        <v>350100007879405</v>
-      </c>
-      <c r="E25" t="str">
-        <v>MOBILE WHOLESALE LTD</v>
-      </c>
-      <c r="F25">
-        <v>293.74</v>
-      </c>
-      <c r="G25">
-        <v>396.34</v>
-      </c>
-      <c r="H25">
-        <v>102.59999999999997</v>
-      </c>
-      <c r="I25" t="str">
-        <v/>
-      </c>
-      <c r="J25" t="str">
-        <v/>
-      </c>
-      <c r="K25" t="str">
-        <v/>
-      </c>
-      <c r="L25">
-        <v>8</v>
-      </c>
-      <c r="M25" t="str">
-        <v/>
-      </c>
-      <c r="N25" t="str">
-        <v/>
-      </c>
-      <c r="O25" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="str">
-        <v>2026-07-04</v>
-      </c>
-      <c r="B26" t="str">
-        <v>ONB-5099</v>
-      </c>
-      <c r="C26" t="str">
-        <v>IPH-256GB-BLA</v>
-      </c>
-      <c r="D26" t="str">
-        <v>350100007911081</v>
-      </c>
-      <c r="E26" t="str">
-        <v>PHONEBOX DIRECT</v>
-      </c>
-      <c r="F26">
-        <v>517.1</v>
-      </c>
-      <c r="G26">
-        <v>754.52</v>
-      </c>
-      <c r="H26">
-        <v>237.41999999999996</v>
-      </c>
-      <c r="I26" t="str">
-        <v/>
-      </c>
-      <c r="J26" t="str">
-        <v/>
-      </c>
-      <c r="K26" t="str">
-        <v/>
-      </c>
-      <c r="L26">
-        <v>8</v>
-      </c>
-      <c r="M26" t="str">
-        <v/>
-      </c>
-      <c r="N26" t="str">
-        <v/>
-      </c>
-      <c r="O26" t="str">
+      <c r="P21" t="str">
+        <v/>
+      </c>
+      <c r="Q21" t="str">
+        <v/>
+      </c>
+      <c r="R21" t="str">
+        <v/>
+      </c>
+      <c r="S21" t="str">
         <v/>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:O26"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:S21"/>
   </ignoredErrors>
 </worksheet>
 </file>